--- a/datos/fab_queso_sim.xlsx
+++ b/datos/fab_queso_sim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3644E964-2DFD-4F67-B074-D9B403A8C893}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43653533-5B85-4CD1-86B1-0B3D51C280A4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
   </bookViews>
   <sheets>
     <sheet name="fab_queso_sim" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -771,7 +771,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -806,7 +806,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -853,138 +852,33 @@
     <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="65">
+  <dxfs count="23">
     <dxf>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment vertical="center"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1028,27 +922,6 @@
     <dxf>
       <alignment vertical="center"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{DADACEEB-7279-4D6E-B5FC-344BE1874627}"/>
@@ -1062,138 +935,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4483F406-C1F3-24FE-C1F2-4A88259E960B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5048250" y="0"/>
-          <a:ext cx="3533775" cy="3438525"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB8190CB-E522-F2C9-3F3D-4019CB67B890}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="10410825" y="381000"/>
-          <a:ext cx="9410700" cy="3629025"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9709,7 +9450,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEF4566A-639C-45E8-B56D-71F07FA00779}" name="TablaDinámica1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEF4566A-639C-45E8-B56D-71F07FA00779}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
   <location ref="A3:J19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="14" showAll="0">
@@ -10247,7 +9988,7 @@
     <dataField name="Desviación_x000a_total_x000a_(%)" fld="31" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="57">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -10259,7 +10000,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -10271,7 +10012,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -10283,13 +10024,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="19">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="53">
+    <format dxfId="18">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="52">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10298,7 +10039,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10307,7 +10048,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10316,7 +10057,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10325,7 +10066,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10334,7 +10075,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10343,7 +10084,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="46">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10352,7 +10093,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10361,7 +10102,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="44">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10387,7 +10128,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}" name="Tabla2" displayName="Tabla2" ref="A1:T365" totalsRowShown="0">
   <autoFilter ref="A1:T365" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="42"/>
+    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{B99A55EC-062A-41A1-9987-66C4A77606BA}" name="entrada_kg"/>
     <tableColumn id="3" xr3:uid="{DA11BF6E-5AFF-4E5A-A825-C843AA73522C}" name="entrada_litros"/>
     <tableColumn id="4" xr3:uid="{ED230348-1BB5-43D8-ADE4-81312B15A5A9}" name="entrada_grasa_g_l"/>
@@ -10399,28 +10140,28 @@
     <tableColumn id="10" xr3:uid="{E2106BDF-6A85-4EF5-B55C-0D7CFEBF9BD8}" name="queso_kg"/>
     <tableColumn id="11" xr3:uid="{8A9920A8-F994-40CF-861E-A78626F5DFA0}" name="queso_est_pct"/>
     <tableColumn id="12" xr3:uid="{7BEF460E-C8FD-436F-A522-912A1E3FC0C1}" name="queso_mg_pct"/>
-    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="64">
+    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="7">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="63">
+    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="6">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="62">
+    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="5">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="61">
+    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="4">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="43">
+    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="3">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="60">
+    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="2">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_mg_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="59">
+    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="1">
       <calculatedColumnFormula>_xlfn.ISOWEEKNUM(Tabla2[[#This Row],[fecha]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="58"/>
+    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10857,7 +10598,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="22">
+      <c r="Q2">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -10926,7 +10667,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>180.31849</v>
       </c>
-      <c r="Q3" s="22">
+      <c r="Q3">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.86489699999998</v>
       </c>
@@ -10995,7 +10736,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>179.89500000000001</v>
       </c>
-      <c r="Q4" s="22">
+      <c r="Q4">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.99867</v>
       </c>
@@ -11064,7 +10805,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.00873000000001</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.48241499999995</v>
       </c>
@@ -11133,7 +10874,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.50821999999999</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.06479999999999</v>
       </c>
@@ -11187,7 +10928,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>195.16079999999999</v>
       </c>
-      <c r="Q7" s="22">
+      <c r="Q7">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>340.94821500000006</v>
       </c>
@@ -11223,7 +10964,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="22">
+      <c r="Q8">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -11274,7 +11015,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="22">
+      <c r="Q9">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -11343,7 +11084,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.8991</v>
       </c>
-      <c r="Q10" s="22">
+      <c r="Q10">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>306.54863700000004</v>
       </c>
@@ -11412,7 +11153,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.35904000000002</v>
       </c>
-      <c r="Q11" s="22">
+      <c r="Q11">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>323.06771200000003</v>
       </c>
@@ -11481,7 +11222,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.54939999999999</v>
       </c>
-      <c r="Q12" s="22">
+      <c r="Q12">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.49744299999998</v>
       </c>
@@ -11550,7 +11291,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.50129999999999</v>
       </c>
-      <c r="Q13" s="22">
+      <c r="Q13">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.48682699999995</v>
       </c>
@@ -11604,7 +11345,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>218.60640000000004</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>387.9083</v>
       </c>
@@ -11640,7 +11381,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="22">
+      <c r="Q15">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -11691,7 +11432,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q16" s="22">
+      <c r="Q16">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -11760,7 +11501,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.74655999999999</v>
       </c>
-      <c r="Q17" s="22">
+      <c r="Q17">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.03810399999998</v>
       </c>
@@ -11829,7 +11570,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.87325999999999</v>
       </c>
-      <c r="Q18" s="22">
+      <c r="Q18">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.90581200000003</v>
       </c>
@@ -11898,7 +11639,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.17689999999999</v>
       </c>
-      <c r="Q19" s="22">
+      <c r="Q19">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>317.22380799999996</v>
       </c>
@@ -11967,7 +11708,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.10843999999997</v>
       </c>
-      <c r="Q20" s="22">
+      <c r="Q20">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>335.71466500000002</v>
       </c>
@@ -12021,7 +11762,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>206.29728</v>
       </c>
-      <c r="Q21" s="22">
+      <c r="Q21">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>375.101856</v>
       </c>
@@ -12057,7 +11798,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="22">
+      <c r="Q22">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -12108,7 +11849,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q23" s="22">
+      <c r="Q23">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -12177,7 +11918,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.42239999999998</v>
       </c>
-      <c r="Q24" s="22">
+      <c r="Q24">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>300.159108</v>
       </c>
@@ -12246,7 +11987,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.68940000000001</v>
       </c>
-      <c r="Q25" s="22">
+      <c r="Q25">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.24774400000001</v>
       </c>
@@ -12315,7 +12056,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.49126000000001</v>
       </c>
-      <c r="Q26" s="22">
+      <c r="Q26">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>317.54294899999996</v>
       </c>
@@ -12384,7 +12125,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.36416</v>
       </c>
-      <c r="Q27" s="22">
+      <c r="Q27">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>311.991264</v>
       </c>
@@ -12438,7 +12179,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>151.04544999999999</v>
       </c>
-      <c r="Q28" s="22">
+      <c r="Q28">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>261.717848</v>
       </c>
@@ -12474,7 +12215,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="22">
+      <c r="Q29">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -12525,7 +12266,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="22">
+      <c r="Q30">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -12594,7 +12335,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.80947999999998</v>
       </c>
-      <c r="Q31" s="22">
+      <c r="Q31">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>298.81906399999997</v>
       </c>
@@ -12663,7 +12404,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.73020000000002</v>
       </c>
-      <c r="Q32" s="22">
+      <c r="Q32">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>315.32410499999992</v>
       </c>
@@ -12732,7 +12473,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.04014000000001</v>
       </c>
-      <c r="Q33" s="22">
+      <c r="Q33">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>297.84472200000005</v>
       </c>
@@ -12801,7 +12542,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.40966</v>
       </c>
-      <c r="Q34" s="22">
+      <c r="Q34">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.55273100000005</v>
       </c>
@@ -12855,7 +12596,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>161.05439999999999</v>
       </c>
-      <c r="Q35" s="22">
+      <c r="Q35">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>284.30212599999999</v>
       </c>
@@ -12891,7 +12632,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q36" s="22">
+      <c r="Q36">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -12942,7 +12683,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q37" s="22">
+      <c r="Q37">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -13011,7 +12752,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.51705000000001</v>
       </c>
-      <c r="Q38" s="22">
+      <c r="Q38">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.20863000000003</v>
       </c>
@@ -13080,7 +12821,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.86541999999997</v>
       </c>
-      <c r="Q39" s="22">
+      <c r="Q39">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.73766599999993</v>
       </c>
@@ -13149,7 +12890,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.6499</v>
       </c>
-      <c r="Q40" s="22">
+      <c r="Q40">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>321.946415</v>
       </c>
@@ -13218,7 +12959,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.55101999999999</v>
       </c>
-      <c r="Q41" s="22">
+      <c r="Q41">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>317.640128</v>
       </c>
@@ -13272,7 +13013,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>151.25344000000001</v>
       </c>
-      <c r="Q42" s="22">
+      <c r="Q42">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>275.07363499999997</v>
       </c>
@@ -13308,7 +13049,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q43" s="22">
+      <c r="Q43">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -13359,7 +13100,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q44" s="22">
+      <c r="Q44">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -13428,7 +13169,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.01918000000001</v>
       </c>
-      <c r="Q45" s="22">
+      <c r="Q45">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>334.20556199999999</v>
       </c>
@@ -13497,7 +13238,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.80865</v>
       </c>
-      <c r="Q46" s="22">
+      <c r="Q46">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.25231500000001</v>
       </c>
@@ -13566,7 +13307,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.44300000000001</v>
       </c>
-      <c r="Q47" s="22">
+      <c r="Q47">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.04498000000001</v>
       </c>
@@ -13635,7 +13376,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.82933000000003</v>
       </c>
-      <c r="Q48" s="22">
+      <c r="Q48">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>283.66286400000001</v>
       </c>
@@ -13689,7 +13430,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>243.46751999999998</v>
       </c>
-      <c r="Q49" s="22">
+      <c r="Q49">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>442.04370600000004</v>
       </c>
@@ -13725,7 +13466,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q50" s="22">
+      <c r="Q50">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -13776,7 +13517,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q51" s="22">
+      <c r="Q51">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -13845,7 +13586,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.04774000000003</v>
       </c>
-      <c r="Q52" s="22">
+      <c r="Q52">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>294.90070200000002</v>
       </c>
@@ -13914,7 +13655,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.46600000000001</v>
       </c>
-      <c r="Q53" s="22">
+      <c r="Q53">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>315.35933000000006</v>
       </c>
@@ -13983,7 +13724,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.178</v>
       </c>
-      <c r="Q54" s="22">
+      <c r="Q54">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>316.13699699999995</v>
       </c>
@@ -14052,7 +13793,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>164.8528</v>
       </c>
-      <c r="Q55" s="22">
+      <c r="Q55">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>286.925276</v>
       </c>
@@ -14106,7 +13847,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>147.19499999999999</v>
       </c>
-      <c r="Q56" s="22">
+      <c r="Q56">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>288.27954</v>
       </c>
@@ -14142,7 +13883,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q57" s="22">
+      <c r="Q57">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -14193,7 +13934,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="22">
+      <c r="Q58">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -14262,7 +14003,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.95337999999998</v>
       </c>
-      <c r="Q59" s="22">
+      <c r="Q59">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>294.99169799999999</v>
       </c>
@@ -14331,7 +14072,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.03049000000001</v>
       </c>
-      <c r="Q60" s="22">
+      <c r="Q60">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.71602200000007</v>
       </c>
@@ -14400,7 +14141,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.41408000000001</v>
       </c>
-      <c r="Q61" s="22">
+      <c r="Q61">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>288.15526999999997</v>
       </c>
@@ -14469,7 +14210,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.16996</v>
       </c>
-      <c r="Q62" s="22">
+      <c r="Q62">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>334.80329400000005</v>
       </c>
@@ -14523,7 +14264,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>105.83789</v>
       </c>
-      <c r="Q63" s="22">
+      <c r="Q63">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>209.19094699999997</v>
       </c>
@@ -14559,7 +14300,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q64" s="22">
+      <c r="Q64">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -14610,7 +14351,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q65" s="22">
+      <c r="Q65">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -14679,7 +14420,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.48828</v>
       </c>
-      <c r="Q66" s="22">
+      <c r="Q66">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.70662799999997</v>
       </c>
@@ -14748,7 +14489,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.37556000000001</v>
       </c>
-      <c r="Q67" s="22">
+      <c r="Q67">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>315.33957000000004</v>
       </c>
@@ -14817,7 +14558,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.1301</v>
       </c>
-      <c r="Q68" s="22">
+      <c r="Q68">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>315.61498499999999</v>
       </c>
@@ -14886,7 +14627,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.31232</v>
       </c>
-      <c r="Q69" s="22">
+      <c r="Q69">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>293.27855999999997</v>
       </c>
@@ -14940,7 +14681,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>141.72543999999999</v>
       </c>
-      <c r="Q70" s="22">
+      <c r="Q70">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>263.03376000000003</v>
       </c>
@@ -14976,7 +14717,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q71" s="22">
+      <c r="Q71">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -15027,7 +14768,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q72" s="22">
+      <c r="Q72">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -15096,7 +14837,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>163.60499999999999</v>
       </c>
-      <c r="Q73" s="22">
+      <c r="Q73">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.84832900000004</v>
       </c>
@@ -15165,7 +14906,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.75581</v>
       </c>
-      <c r="Q74" s="22">
+      <c r="Q74">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.32890900000001</v>
       </c>
@@ -15234,7 +14975,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.11264</v>
       </c>
-      <c r="Q75" s="22">
+      <c r="Q75">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>316.29139200000003</v>
       </c>
@@ -15303,7 +15044,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.98074999999997</v>
       </c>
-      <c r="Q76" s="22">
+      <c r="Q76">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>300.22355999999996</v>
       </c>
@@ -15357,7 +15098,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>146.06</v>
       </c>
-      <c r="Q77" s="22">
+      <c r="Q77">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>270.48288300000002</v>
       </c>
@@ -15393,7 +15134,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q78" s="22">
+      <c r="Q78">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -15444,7 +15185,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q79" s="22">
+      <c r="Q79">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -15513,7 +15254,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.79556000000002</v>
       </c>
-      <c r="Q80" s="22">
+      <c r="Q80">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.451414</v>
       </c>
@@ -15582,7 +15323,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.4727</v>
       </c>
-      <c r="Q81" s="22">
+      <c r="Q81">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>296.86415</v>
       </c>
@@ -15651,7 +15392,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.31381999999996</v>
       </c>
-      <c r="Q82" s="22">
+      <c r="Q82">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>308.43467200000003</v>
       </c>
@@ -15720,7 +15461,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.49069999999998</v>
       </c>
-      <c r="Q83" s="22">
+      <c r="Q83">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>298.36753100000004</v>
       </c>
@@ -15774,7 +15515,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>153.72756000000001</v>
       </c>
-      <c r="Q84" s="22">
+      <c r="Q84">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>270.88812000000001</v>
       </c>
@@ -15810,7 +15551,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q85" s="22">
+      <c r="Q85">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -15861,7 +15602,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q86" s="22">
+      <c r="Q86">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -15930,7 +15671,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.13579999999999</v>
       </c>
-      <c r="Q87" s="22">
+      <c r="Q87">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>290.859486</v>
       </c>
@@ -15999,7 +15740,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.93425999999997</v>
       </c>
-      <c r="Q88" s="22">
+      <c r="Q88">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>317.27373599999999</v>
       </c>
@@ -16068,7 +15809,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.36609999999999</v>
       </c>
-      <c r="Q89" s="22">
+      <c r="Q89">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.67391499999997</v>
       </c>
@@ -16137,7 +15878,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.63560000000001</v>
       </c>
-      <c r="Q90" s="22">
+      <c r="Q90">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>293.33331000000004</v>
       </c>
@@ -16191,7 +15932,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>200.35544999999999</v>
       </c>
-      <c r="Q91" s="22">
+      <c r="Q91">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>336.59479200000004</v>
       </c>
@@ -16227,7 +15968,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q92" s="22">
+      <c r="Q92">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -16278,7 +16019,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q93" s="22">
+      <c r="Q93">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -16347,7 +16088,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.36252999999999</v>
       </c>
-      <c r="Q94" s="22">
+      <c r="Q94">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>287.95120200000002</v>
       </c>
@@ -16416,7 +16157,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.82854</v>
       </c>
-      <c r="Q95" s="22">
+      <c r="Q95">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.23394199999996</v>
       </c>
@@ -16485,7 +16226,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.85</v>
       </c>
-      <c r="Q96" s="22">
+      <c r="Q96">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>326.22625599999998</v>
       </c>
@@ -16554,7 +16295,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.78941999999998</v>
       </c>
-      <c r="Q97" s="22">
+      <c r="Q97">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>296.52183599999995</v>
       </c>
@@ -16608,7 +16349,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.69254000000001</v>
       </c>
-      <c r="Q98" s="22">
+      <c r="Q98">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>291.36320799999999</v>
       </c>
@@ -16644,7 +16385,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q99" s="22">
+      <c r="Q99">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -16695,7 +16436,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q100" s="22">
+      <c r="Q100">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -16764,7 +16505,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.59443999999996</v>
       </c>
-      <c r="Q101" s="22">
+      <c r="Q101">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>307.77028799999994</v>
       </c>
@@ -16833,7 +16574,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.53217999999998</v>
       </c>
-      <c r="Q102" s="22">
+      <c r="Q102">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>308.00425000000001</v>
       </c>
@@ -16902,7 +16643,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.81861999999998</v>
       </c>
-      <c r="Q103" s="22">
+      <c r="Q103">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>327.85602</v>
       </c>
@@ -16971,7 +16712,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.054</v>
       </c>
-      <c r="Q104" s="22">
+      <c r="Q104">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>292.68566400000003</v>
       </c>
@@ -17025,7 +16766,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>125.03988000000001</v>
       </c>
-      <c r="Q105" s="22">
+      <c r="Q105">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>234.19096399999998</v>
       </c>
@@ -17061,7 +16802,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q106" s="22">
+      <c r="Q106">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -17112,7 +16853,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q107" s="22">
+      <c r="Q107">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -17181,7 +16922,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.80120000000002</v>
       </c>
-      <c r="Q108" s="22">
+      <c r="Q108">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.98919799999999</v>
       </c>
@@ -17250,7 +16991,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.28310999999999</v>
       </c>
-      <c r="Q109" s="22">
+      <c r="Q109">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>319.52921200000003</v>
       </c>
@@ -17319,7 +17060,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.72231999999997</v>
       </c>
-      <c r="Q110" s="22">
+      <c r="Q110">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.69026400000001</v>
       </c>
@@ -17388,7 +17129,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.98599999999999</v>
       </c>
-      <c r="Q111" s="22">
+      <c r="Q111">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.08353999999997</v>
       </c>
@@ -17442,7 +17183,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.82363999999998</v>
       </c>
-      <c r="Q112" s="22">
+      <c r="Q112">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>292.87780200000003</v>
       </c>
@@ -17478,7 +17219,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q113" s="22">
+      <c r="Q113">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -17529,7 +17270,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q114" s="22">
+      <c r="Q114">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -17598,7 +17339,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.85569999999998</v>
       </c>
-      <c r="Q115" s="22">
+      <c r="Q115">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>300.35292800000002</v>
       </c>
@@ -17667,7 +17408,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>177.69319000000002</v>
       </c>
-      <c r="Q116" s="22">
+      <c r="Q116">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.060205</v>
       </c>
@@ -17736,7 +17477,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.9051</v>
       </c>
-      <c r="Q117" s="22">
+      <c r="Q117">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.50019800000001</v>
       </c>
@@ -17805,7 +17546,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>178.9171</v>
       </c>
-      <c r="Q118" s="22">
+      <c r="Q118">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>328.36831999999993</v>
       </c>
@@ -17859,7 +17600,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>164.99231</v>
       </c>
-      <c r="Q119" s="22">
+      <c r="Q119">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>288.52091999999999</v>
       </c>
@@ -17895,7 +17636,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q120" s="22">
+      <c r="Q120">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -17946,7 +17687,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q121" s="22">
+      <c r="Q121">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -18015,7 +17756,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>179.15583999999998</v>
       </c>
-      <c r="Q122" s="22">
+      <c r="Q122">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>311.041696</v>
       </c>
@@ -18084,7 +17825,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.44039999999998</v>
       </c>
-      <c r="Q123" s="22">
+      <c r="Q123">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>297.69246399999997</v>
       </c>
@@ -18153,7 +17894,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.06126999999998</v>
       </c>
-      <c r="Q124" s="22">
+      <c r="Q124">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.94915999999995</v>
       </c>
@@ -18222,7 +17963,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.88090000000003</v>
       </c>
-      <c r="Q125" s="22">
+      <c r="Q125">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.87559999999996</v>
       </c>
@@ -18276,7 +18017,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>192.60300000000001</v>
       </c>
-      <c r="Q126" s="22">
+      <c r="Q126">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>365.25035699999995</v>
       </c>
@@ -18312,7 +18053,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q127" s="22">
+      <c r="Q127">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -18363,7 +18104,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q128" s="22">
+      <c r="Q128">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -18432,7 +18173,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.59759999999997</v>
       </c>
-      <c r="Q129" s="22">
+      <c r="Q129">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>306.22107999999997</v>
       </c>
@@ -18501,7 +18242,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.53779</v>
       </c>
-      <c r="Q130" s="22">
+      <c r="Q130">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.83238</v>
       </c>
@@ -18570,7 +18311,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.41848000000002</v>
       </c>
-      <c r="Q131" s="22">
+      <c r="Q131">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.02731799999998</v>
       </c>
@@ -18639,7 +18380,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.26488000000001</v>
       </c>
-      <c r="Q132" s="22">
+      <c r="Q132">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>305.37106899999998</v>
       </c>
@@ -18693,7 +18434,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>179.77782000000002</v>
       </c>
-      <c r="Q133" s="22">
+      <c r="Q133">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>329.75341000000003</v>
       </c>
@@ -18729,7 +18470,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q134" s="22">
+      <c r="Q134">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -18780,7 +18521,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q135" s="22">
+      <c r="Q135">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -18849,7 +18590,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.23712000000003</v>
       </c>
-      <c r="Q136" s="22">
+      <c r="Q136">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>296.824164</v>
       </c>
@@ -18918,7 +18659,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.15415999999999</v>
       </c>
-      <c r="Q137" s="22">
+      <c r="Q137">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.05250100000006</v>
       </c>
@@ -18987,7 +18728,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.94150999999999</v>
       </c>
-      <c r="Q138" s="22">
+      <c r="Q138">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>307.88596799999999</v>
       </c>
@@ -19056,7 +18797,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.14122</v>
       </c>
-      <c r="Q139" s="22">
+      <c r="Q139">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.34414500000003</v>
       </c>
@@ -19110,7 +18851,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.56128000000001</v>
       </c>
-      <c r="Q140" s="22">
+      <c r="Q140">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>308.54831799999999</v>
       </c>
@@ -19146,7 +18887,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q141" s="22">
+      <c r="Q141">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -19197,7 +18938,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q142" s="22">
+      <c r="Q142">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -19266,7 +19007,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.82854</v>
       </c>
-      <c r="Q143" s="22">
+      <c r="Q143">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>306.58225000000004</v>
       </c>
@@ -19335,7 +19076,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.92919000000001</v>
       </c>
-      <c r="Q144" s="22">
+      <c r="Q144">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.31288699999999</v>
       </c>
@@ -19404,7 +19145,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.60564000000002</v>
       </c>
-      <c r="Q145" s="22">
+      <c r="Q145">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>311.39461000000006</v>
       </c>
@@ -19473,7 +19214,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.91865999999999</v>
       </c>
-      <c r="Q146" s="22">
+      <c r="Q146">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.11743000000001</v>
       </c>
@@ -19527,7 +19268,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>148.73088000000001</v>
       </c>
-      <c r="Q147" s="22">
+      <c r="Q147">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>273.32406599999996</v>
       </c>
@@ -19563,7 +19304,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q148" s="22">
+      <c r="Q148">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -19614,7 +19355,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q149" s="22">
+      <c r="Q149">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -19683,7 +19424,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.00685999999999</v>
       </c>
-      <c r="Q150" s="22">
+      <c r="Q150">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>337.90796999999998</v>
       </c>
@@ -19752,7 +19493,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.19219999999999</v>
       </c>
-      <c r="Q151" s="22">
+      <c r="Q151">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>322.50765000000001</v>
       </c>
@@ -19821,7 +19562,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.649</v>
       </c>
-      <c r="Q152" s="22">
+      <c r="Q152">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>319.82082600000001</v>
       </c>
@@ -19890,7 +19631,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.64400000000001</v>
       </c>
-      <c r="Q153" s="22">
+      <c r="Q153">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>321.52760999999998</v>
       </c>
@@ -19944,7 +19685,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>156.5095</v>
       </c>
-      <c r="Q154" s="22">
+      <c r="Q154">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>285.04331399999995</v>
       </c>
@@ -19980,7 +19721,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q155" s="22">
+      <c r="Q155">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -20031,7 +19772,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q156" s="22">
+      <c r="Q156">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -20100,7 +19841,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.16398000000001</v>
       </c>
-      <c r="Q157" s="22">
+      <c r="Q157">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>298.570761</v>
       </c>
@@ -20169,7 +19910,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.54257999999999</v>
       </c>
-      <c r="Q158" s="22">
+      <c r="Q158">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.57291900000001</v>
       </c>
@@ -20238,7 +19979,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.48061999999999</v>
       </c>
-      <c r="Q159" s="22">
+      <c r="Q159">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>317.40009599999996</v>
       </c>
@@ -20307,7 +20048,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.47300000000001</v>
       </c>
-      <c r="Q160" s="22">
+      <c r="Q160">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.74223999999992</v>
       </c>
@@ -20361,7 +20102,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>154.73339999999999</v>
       </c>
-      <c r="Q161" s="22">
+      <c r="Q161">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>266.07095999999996</v>
       </c>
@@ -20397,7 +20138,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q162" s="22">
+      <c r="Q162">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -20448,7 +20189,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q163" s="22">
+      <c r="Q163">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -20517,7 +20258,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.35714000000002</v>
       </c>
-      <c r="Q164" s="22">
+      <c r="Q164">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>307.95287500000001</v>
       </c>
@@ -20586,7 +20327,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.15890000000002</v>
       </c>
-      <c r="Q165" s="22">
+      <c r="Q165">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>321.44712599999997</v>
       </c>
@@ -20655,7 +20396,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>164.68451999999999</v>
       </c>
-      <c r="Q166" s="22">
+      <c r="Q166">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>308.85596599999997</v>
       </c>
@@ -20724,7 +20465,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>165.79342000000003</v>
       </c>
-      <c r="Q167" s="22">
+      <c r="Q167">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>338.94638500000002</v>
       </c>
@@ -20778,7 +20519,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>190.51626999999999</v>
       </c>
-      <c r="Q168" s="22">
+      <c r="Q168">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>348.69437100000005</v>
       </c>
@@ -20814,7 +20555,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q169" s="22">
+      <c r="Q169">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -20865,7 +20606,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q170" s="22">
+      <c r="Q170">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -20934,7 +20675,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.70392999999999</v>
       </c>
-      <c r="Q171" s="22">
+      <c r="Q171">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>327.47180399999996</v>
       </c>
@@ -21003,7 +20744,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.07132000000001</v>
       </c>
-      <c r="Q172" s="22">
+      <c r="Q172">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.16477800000001</v>
       </c>
@@ -21072,7 +20813,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>179.22167999999999</v>
       </c>
-      <c r="Q173" s="22">
+      <c r="Q173">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.50006299999995</v>
       </c>
@@ -21141,7 +20882,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.76485</v>
       </c>
-      <c r="Q174" s="22">
+      <c r="Q174">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>317.39630400000004</v>
       </c>
@@ -21195,7 +20936,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>196.80627999999999</v>
       </c>
-      <c r="Q175" s="22">
+      <c r="Q175">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>343.51996200000002</v>
       </c>
@@ -21231,7 +20972,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q176" s="22">
+      <c r="Q176">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -21282,7 +21023,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q177" s="22">
+      <c r="Q177">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -21351,7 +21092,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.69998999999999</v>
       </c>
-      <c r="Q178" s="22">
+      <c r="Q178">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.45499999999998</v>
       </c>
@@ -21420,7 +21161,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.6378</v>
       </c>
-      <c r="Q179" s="22">
+      <c r="Q179">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>306.20133999999996</v>
       </c>
@@ -21489,7 +21230,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.72874999999999</v>
       </c>
-      <c r="Q180" s="22">
+      <c r="Q180">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>291.87752</v>
       </c>
@@ -21558,7 +21299,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.17599999999999</v>
       </c>
-      <c r="Q181" s="22">
+      <c r="Q181">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>316.76142700000003</v>
       </c>
@@ -21612,7 +21353,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.05929999999998</v>
       </c>
-      <c r="Q182" s="22">
+      <c r="Q182">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>311.33459500000004</v>
       </c>
@@ -21648,7 +21389,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q183" s="22">
+      <c r="Q183">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -21699,7 +21440,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q184" s="22">
+      <c r="Q184">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -21768,7 +21509,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.01314000000002</v>
       </c>
-      <c r="Q185" s="22">
+      <c r="Q185">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.47505000000001</v>
       </c>
@@ -21837,7 +21578,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.99909999999997</v>
       </c>
-      <c r="Q186" s="22">
+      <c r="Q186">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.20612</v>
       </c>
@@ -21906,7 +21647,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.73079999999999</v>
       </c>
-      <c r="Q187" s="22">
+      <c r="Q187">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>304.83221000000003</v>
       </c>
@@ -21975,7 +21716,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.77975000000001</v>
       </c>
-      <c r="Q188" s="22">
+      <c r="Q188">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>320.312592</v>
       </c>
@@ -22029,7 +21770,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>162.32433</v>
       </c>
-      <c r="Q189" s="22">
+      <c r="Q189">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.05207999999999</v>
       </c>
@@ -22065,7 +21806,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q190" s="22">
+      <c r="Q190">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -22116,7 +21857,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q191" s="22">
+      <c r="Q191">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -22185,7 +21926,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.15890000000002</v>
       </c>
-      <c r="Q192" s="22">
+      <c r="Q192">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.47215999999997</v>
       </c>
@@ -22254,7 +21995,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.48712</v>
       </c>
-      <c r="Q193" s="22">
+      <c r="Q193">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>315.36050399999999</v>
       </c>
@@ -22323,7 +22064,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.9194</v>
       </c>
-      <c r="Q194" s="22">
+      <c r="Q194">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.19847100000004</v>
       </c>
@@ -22392,7 +22133,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.93583999999998</v>
       </c>
-      <c r="Q195" s="22">
+      <c r="Q195">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>295.8279</v>
       </c>
@@ -22446,7 +22187,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>221.91932</v>
       </c>
-      <c r="Q196" s="22">
+      <c r="Q196">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>377.85504500000002</v>
       </c>
@@ -22482,7 +22223,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q197" s="22">
+      <c r="Q197">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -22533,7 +22274,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q198" s="22">
+      <c r="Q198">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -22602,7 +22343,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>177.84960000000001</v>
       </c>
-      <c r="Q199" s="22">
+      <c r="Q199">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>323.13403200000005</v>
       </c>
@@ -22671,7 +22412,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.62266</v>
       </c>
-      <c r="Q200" s="22">
+      <c r="Q200">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.45249000000001</v>
       </c>
@@ -22740,7 +22481,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.86163999999999</v>
       </c>
-      <c r="Q201" s="22">
+      <c r="Q201">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.69316400000002</v>
       </c>
@@ -22809,7 +22550,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>177.1354</v>
       </c>
-      <c r="Q202" s="22">
+      <c r="Q202">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.68035200000003</v>
       </c>
@@ -22863,7 +22604,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>214.53233999999998</v>
       </c>
-      <c r="Q203" s="22">
+      <c r="Q203">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>386.59868799999998</v>
       </c>
@@ -22899,7 +22640,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q204" s="22">
+      <c r="Q204">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -22950,7 +22691,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q205" s="22">
+      <c r="Q205">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -23019,7 +22760,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.23061999999999</v>
       </c>
-      <c r="Q206" s="22">
+      <c r="Q206">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.51009999999997</v>
       </c>
@@ -23088,7 +22829,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.78995999999998</v>
       </c>
-      <c r="Q207" s="22">
+      <c r="Q207">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>298.11462399999999</v>
       </c>
@@ -23157,7 +22898,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.20175</v>
       </c>
-      <c r="Q208" s="22">
+      <c r="Q208">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.64164</v>
       </c>
@@ -23226,7 +22967,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.45548000000002</v>
       </c>
-      <c r="Q209" s="22">
+      <c r="Q209">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>300.23495100000002</v>
       </c>
@@ -23280,7 +23021,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>157.97475</v>
       </c>
-      <c r="Q210" s="22">
+      <c r="Q210">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>276.98101200000002</v>
       </c>
@@ -23316,7 +23057,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q211" s="22">
+      <c r="Q211">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -23367,7 +23108,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q212" s="22">
+      <c r="Q212">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -23436,7 +23177,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.60906000000003</v>
       </c>
-      <c r="Q213" s="22">
+      <c r="Q213">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>304.974917</v>
       </c>
@@ -23505,7 +23246,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.35249999999999</v>
       </c>
-      <c r="Q214" s="22">
+      <c r="Q214">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>320.44930399999998</v>
       </c>
@@ -23574,7 +23315,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.18299999999999</v>
       </c>
-      <c r="Q215" s="22">
+      <c r="Q215">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.26455999999996</v>
       </c>
@@ -23643,7 +23384,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.65045000000001</v>
       </c>
-      <c r="Q216" s="22">
+      <c r="Q216">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.29727200000002</v>
       </c>
@@ -23697,7 +23438,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>157.22854000000001</v>
       </c>
-      <c r="Q217" s="22">
+      <c r="Q217">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>283.72100400000005</v>
       </c>
@@ -23733,7 +23474,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q218" s="22">
+      <c r="Q218">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -23784,7 +23525,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q219" s="22">
+      <c r="Q219">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -23853,7 +23594,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.72716999999997</v>
       </c>
-      <c r="Q220" s="22">
+      <c r="Q220">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>295.400105</v>
       </c>
@@ -23922,7 +23663,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.67775999999998</v>
       </c>
-      <c r="Q221" s="22">
+      <c r="Q221">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>308.75949800000001</v>
       </c>
@@ -23991,7 +23732,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.14975999999999</v>
       </c>
-      <c r="Q222" s="22">
+      <c r="Q222">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.63360399999999</v>
       </c>
@@ -24060,7 +23801,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.00369000000001</v>
       </c>
-      <c r="Q223" s="22">
+      <c r="Q223">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.468052</v>
       </c>
@@ -24114,7 +23855,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>108.25794</v>
       </c>
-      <c r="Q224" s="22">
+      <c r="Q224">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>184.27872599999998</v>
       </c>
@@ -24150,7 +23891,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q225" s="22">
+      <c r="Q225">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -24201,7 +23942,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q226" s="22">
+      <c r="Q226">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -24270,7 +24011,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.4315</v>
       </c>
-      <c r="Q227" s="22">
+      <c r="Q227">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>329.16177499999998</v>
       </c>
@@ -24339,7 +24080,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.93946</v>
       </c>
-      <c r="Q228" s="22">
+      <c r="Q228">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.00382000000002</v>
       </c>
@@ -24408,7 +24149,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.42099999999999</v>
       </c>
-      <c r="Q229" s="22">
+      <c r="Q229">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.27670200000006</v>
       </c>
@@ -24477,7 +24218,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.91667999999999</v>
       </c>
-      <c r="Q230" s="22">
+      <c r="Q230">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>305.970372</v>
       </c>
@@ -24531,7 +24272,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.22248000000002</v>
       </c>
-      <c r="Q231" s="22">
+      <c r="Q231">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.59525400000001</v>
       </c>
@@ -24567,7 +24308,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q232" s="22">
+      <c r="Q232">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -24618,7 +24359,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q233" s="22">
+      <c r="Q233">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -24687,7 +24428,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.46039999999999</v>
       </c>
-      <c r="Q234" s="22">
+      <c r="Q234">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.41502600000001</v>
       </c>
@@ -24756,7 +24497,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.56960000000001</v>
       </c>
-      <c r="Q235" s="22">
+      <c r="Q235">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.11389600000001</v>
       </c>
@@ -24825,7 +24566,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.8186</v>
       </c>
-      <c r="Q236" s="22">
+      <c r="Q236">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>287.62047999999999</v>
       </c>
@@ -24894,7 +24635,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.97372000000001</v>
       </c>
-      <c r="Q237" s="22">
+      <c r="Q237">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>297.73619400000001</v>
       </c>
@@ -24948,7 +24689,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>159.54906</v>
       </c>
-      <c r="Q238" s="22">
+      <c r="Q238">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>291.796469</v>
       </c>
@@ -24984,7 +24725,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q239" s="22">
+      <c r="Q239">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -25035,7 +24776,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q240" s="22">
+      <c r="Q240">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -25104,7 +24845,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.6378</v>
       </c>
-      <c r="Q241" s="22">
+      <c r="Q241">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.50692000000004</v>
       </c>
@@ -25173,7 +24914,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.78040000000001</v>
       </c>
-      <c r="Q242" s="22">
+      <c r="Q242">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>303.58561200000003</v>
       </c>
@@ -25242,7 +24983,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.71072000000001</v>
       </c>
-      <c r="Q243" s="22">
+      <c r="Q243">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>319.58390100000003</v>
       </c>
@@ -25311,7 +25052,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.53918999999999</v>
       </c>
-      <c r="Q244" s="22">
+      <c r="Q244">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.30115599999999</v>
       </c>
@@ -25365,7 +25106,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>153.89419000000001</v>
       </c>
-      <c r="Q245" s="22">
+      <c r="Q245">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>277.41475499999996</v>
       </c>
@@ -25401,7 +25142,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q246" s="22">
+      <c r="Q246">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -25452,7 +25193,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q247" s="22">
+      <c r="Q247">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -25521,7 +25262,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.34464</v>
       </c>
-      <c r="Q248" s="22">
+      <c r="Q248">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.025464</v>
       </c>
@@ -25590,7 +25331,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.99668000000003</v>
       </c>
-      <c r="Q249" s="22">
+      <c r="Q249">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>290.327832</v>
       </c>
@@ -25659,7 +25400,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.19296000000003</v>
       </c>
-      <c r="Q250" s="22">
+      <c r="Q250">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>299.44028400000002</v>
       </c>
@@ -25728,7 +25469,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.39774999999997</v>
       </c>
-      <c r="Q251" s="22">
+      <c r="Q251">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>331.02339199999994</v>
       </c>
@@ -25782,7 +25523,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>130.02170999999998</v>
       </c>
-      <c r="Q252" s="22">
+      <c r="Q252">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>229.90438399999999</v>
       </c>
@@ -25818,7 +25559,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q253" s="22">
+      <c r="Q253">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -25869,7 +25610,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q254" s="22">
+      <c r="Q254">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -25938,7 +25679,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>177.54816</v>
       </c>
-      <c r="Q255" s="22">
+      <c r="Q255">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.258152</v>
       </c>
@@ -26007,7 +25748,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.80224000000001</v>
       </c>
-      <c r="Q256" s="22">
+      <c r="Q256">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>276.231177</v>
       </c>
@@ -26076,7 +25817,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.60329999999999</v>
       </c>
-      <c r="Q257" s="22">
+      <c r="Q257">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.497409</v>
       </c>
@@ -26145,7 +25886,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.67487999999997</v>
       </c>
-      <c r="Q258" s="22">
+      <c r="Q258">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>316.40519999999998</v>
       </c>
@@ -26199,7 +25940,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>160.67250000000001</v>
       </c>
-      <c r="Q259" s="22">
+      <c r="Q259">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>287.25763000000001</v>
       </c>
@@ -26235,7 +25976,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q260" s="22">
+      <c r="Q260">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -26286,7 +26027,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q261" s="22">
+      <c r="Q261">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -26355,7 +26096,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.5744</v>
       </c>
-      <c r="Q262" s="22">
+      <c r="Q262">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>329.38151499999998</v>
       </c>
@@ -26424,7 +26165,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.73479999999998</v>
       </c>
-      <c r="Q263" s="22">
+      <c r="Q263">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.21372999999994</v>
       </c>
@@ -26493,7 +26234,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.09074000000001</v>
       </c>
-      <c r="Q264" s="22">
+      <c r="Q264">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.57350400000001</v>
       </c>
@@ -26562,7 +26303,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>165.55644000000001</v>
       </c>
-      <c r="Q265" s="22">
+      <c r="Q265">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.18302</v>
       </c>
@@ -26616,7 +26357,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.81107</v>
       </c>
-      <c r="Q266" s="22">
+      <c r="Q266">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>329.28043000000002</v>
       </c>
@@ -26652,7 +26393,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q267" s="22">
+      <c r="Q267">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -26703,7 +26444,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q268" s="22">
+      <c r="Q268">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -26772,7 +26513,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.61098000000001</v>
       </c>
-      <c r="Q269" s="22">
+      <c r="Q269">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>314.02285499999994</v>
       </c>
@@ -26841,7 +26582,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.28718000000001</v>
       </c>
-      <c r="Q270" s="22">
+      <c r="Q270">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>322.19748599999997</v>
       </c>
@@ -26910,7 +26651,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.91167999999999</v>
       </c>
-      <c r="Q271" s="22">
+      <c r="Q271">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.44945600000005</v>
       </c>
@@ -26979,7 +26720,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.35833</v>
       </c>
-      <c r="Q272" s="22">
+      <c r="Q272">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.85619999999994</v>
       </c>
@@ -27033,7 +26774,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>191.59140000000002</v>
       </c>
-      <c r="Q273" s="22">
+      <c r="Q273">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>357.03544499999998</v>
       </c>
@@ -27069,7 +26810,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q274" s="22">
+      <c r="Q274">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -27120,7 +26861,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q275" s="22">
+      <c r="Q275">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -27189,7 +26930,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.72660000000002</v>
       </c>
-      <c r="Q276" s="22">
+      <c r="Q276">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.10578300000003</v>
       </c>
@@ -27258,7 +26999,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.91499999999999</v>
       </c>
-      <c r="Q277" s="22">
+      <c r="Q277">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>297.47307799999999</v>
       </c>
@@ -27327,7 +27068,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.00623999999999</v>
       </c>
-      <c r="Q278" s="22">
+      <c r="Q278">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>304.56160899999998</v>
       </c>
@@ -27396,7 +27137,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.86624</v>
       </c>
-      <c r="Q279" s="22">
+      <c r="Q279">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.36451299999999</v>
       </c>
@@ -27450,7 +27191,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>175.9632</v>
       </c>
-      <c r="Q280" s="22">
+      <c r="Q280">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>326.14987500000001</v>
       </c>
@@ -27486,7 +27227,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q281" s="22">
+      <c r="Q281">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -27537,7 +27278,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q282" s="22">
+      <c r="Q282">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -27606,7 +27347,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.71692000000002</v>
       </c>
-      <c r="Q283" s="22">
+      <c r="Q283">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>320.98411800000002</v>
       </c>
@@ -27675,7 +27416,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.52178000000001</v>
       </c>
-      <c r="Q284" s="22">
+      <c r="Q284">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.49340999999998</v>
       </c>
@@ -27744,7 +27485,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.58140000000003</v>
       </c>
-      <c r="Q285" s="22">
+      <c r="Q285">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>306.38069999999999</v>
       </c>
@@ -27813,7 +27554,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>164.65175999999997</v>
       </c>
-      <c r="Q286" s="22">
+      <c r="Q286">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>307.72818000000001</v>
       </c>
@@ -27867,7 +27608,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>163.78752000000003</v>
       </c>
-      <c r="Q287" s="22">
+      <c r="Q287">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.44822600000003</v>
       </c>
@@ -27903,7 +27644,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q288" s="22">
+      <c r="Q288">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -27954,7 +27695,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q289" s="22">
+      <c r="Q289">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -28023,7 +27764,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.33056999999999</v>
       </c>
-      <c r="Q290" s="22">
+      <c r="Q290">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.07903800000003</v>
       </c>
@@ -28092,7 +27833,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.54336000000001</v>
       </c>
-      <c r="Q291" s="22">
+      <c r="Q291">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.19079999999997</v>
       </c>
@@ -28161,7 +27902,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.05256000000003</v>
       </c>
-      <c r="Q292" s="22">
+      <c r="Q292">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.49704000000003</v>
       </c>
@@ -28230,7 +27971,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.12625</v>
       </c>
-      <c r="Q293" s="22">
+      <c r="Q293">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>321.19150400000001</v>
       </c>
@@ -28284,7 +28025,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>187.75595999999999</v>
       </c>
-      <c r="Q294" s="22">
+      <c r="Q294">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>333.57794199999995</v>
       </c>
@@ -28320,7 +28061,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q295" s="22">
+      <c r="Q295">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -28371,7 +28112,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q296" s="22">
+      <c r="Q296">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -28440,7 +28181,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.26527999999999</v>
       </c>
-      <c r="Q297" s="22">
+      <c r="Q297">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>321.39113599999996</v>
       </c>
@@ -28509,7 +28250,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.69925000000001</v>
       </c>
-      <c r="Q298" s="22">
+      <c r="Q298">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>295.66405400000002</v>
       </c>
@@ -28578,7 +28319,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.86751999999998</v>
       </c>
-      <c r="Q299" s="22">
+      <c r="Q299">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.59347500000001</v>
       </c>
@@ -28647,7 +28388,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.94886000000002</v>
       </c>
-      <c r="Q300" s="22">
+      <c r="Q300">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.52327200000002</v>
       </c>
@@ -28701,7 +28442,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>161.11428000000001</v>
       </c>
-      <c r="Q301" s="22">
+      <c r="Q301">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>296.31365399999999</v>
       </c>
@@ -28737,7 +28478,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q302" s="22">
+      <c r="Q302">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -28788,7 +28529,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q303" s="22">
+      <c r="Q303">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -28857,7 +28598,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.84704000000002</v>
       </c>
-      <c r="Q304" s="22">
+      <c r="Q304">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>285.85382800000002</v>
       </c>
@@ -28926,7 +28667,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>162.91368</v>
       </c>
-      <c r="Q305" s="22">
+      <c r="Q305">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>304.89558</v>
       </c>
@@ -28995,7 +28736,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.81745999999998</v>
       </c>
-      <c r="Q306" s="22">
+      <c r="Q306">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>323.44878</v>
       </c>
@@ -29064,7 +28805,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.2415</v>
       </c>
-      <c r="Q307" s="22">
+      <c r="Q307">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.97592599999996</v>
       </c>
@@ -29118,7 +28859,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>178.88210999999998</v>
       </c>
-      <c r="Q308" s="22">
+      <c r="Q308">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>322.32456000000008</v>
       </c>
@@ -29154,7 +28895,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q309" s="22">
+      <c r="Q309">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -29205,7 +28946,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q310" s="22">
+      <c r="Q310">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -29274,7 +29015,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.07984000000002</v>
       </c>
-      <c r="Q311" s="22">
+      <c r="Q311">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>304.164784</v>
       </c>
@@ -29343,7 +29084,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.84612999999999</v>
       </c>
-      <c r="Q312" s="22">
+      <c r="Q312">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.71225000000004</v>
       </c>
@@ -29412,7 +29153,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.48824999999999</v>
       </c>
-      <c r="Q313" s="22">
+      <c r="Q313">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>305.83855299999999</v>
       </c>
@@ -29481,7 +29222,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.232</v>
       </c>
-      <c r="Q314" s="22">
+      <c r="Q314">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>316.63989600000002</v>
       </c>
@@ -29535,7 +29276,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>162.35929999999999</v>
       </c>
-      <c r="Q315" s="22">
+      <c r="Q315">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>305.07240400000001</v>
       </c>
@@ -29571,7 +29312,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q316" s="22">
+      <c r="Q316">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -29622,7 +29363,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q317" s="22">
+      <c r="Q317">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -29691,7 +29432,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.25908999999999</v>
       </c>
-      <c r="Q318" s="22">
+      <c r="Q318">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>298.26641699999999</v>
       </c>
@@ -29760,7 +29501,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.63591</v>
       </c>
-      <c r="Q319" s="22">
+      <c r="Q319">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>322.010108</v>
       </c>
@@ -29829,7 +29570,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>166.66314</v>
       </c>
-      <c r="Q320" s="22">
+      <c r="Q320">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>312.790932</v>
       </c>
@@ -29898,7 +29639,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>167.71761999999998</v>
       </c>
-      <c r="Q321" s="22">
+      <c r="Q321">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>291.08916199999999</v>
       </c>
@@ -29952,7 +29693,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>177.2886</v>
       </c>
-      <c r="Q322" s="22">
+      <c r="Q322">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>323.24956800000001</v>
       </c>
@@ -29988,7 +29729,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q323" s="22">
+      <c r="Q323">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -30039,7 +29780,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q324" s="22">
+      <c r="Q324">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -30108,7 +29849,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>179.62924000000001</v>
       </c>
-      <c r="Q325" s="22">
+      <c r="Q325">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>302.07114699999994</v>
       </c>
@@ -30177,7 +29918,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>177.06597999999997</v>
       </c>
-      <c r="Q326" s="22">
+      <c r="Q326">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>300.09306600000002</v>
       </c>
@@ -30246,7 +29987,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.66711999999998</v>
       </c>
-      <c r="Q327" s="22">
+      <c r="Q327">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>287.95486800000003</v>
       </c>
@@ -30315,7 +30056,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.89279999999999</v>
       </c>
-      <c r="Q328" s="22">
+      <c r="Q328">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>295.51870000000002</v>
       </c>
@@ -30369,7 +30110,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>186.34390000000002</v>
       </c>
-      <c r="Q329" s="22">
+      <c r="Q329">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.72420799999998</v>
       </c>
@@ -30405,7 +30146,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q330" s="22">
+      <c r="Q330">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -30456,7 +30197,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q331" s="22">
+      <c r="Q331">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -30525,7 +30266,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.23688000000001</v>
       </c>
-      <c r="Q332" s="22">
+      <c r="Q332">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.88152500000001</v>
       </c>
@@ -30594,7 +30335,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.05707000000001</v>
       </c>
-      <c r="Q333" s="22">
+      <c r="Q333">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>309.78547500000002</v>
       </c>
@@ -30663,7 +30404,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.65360000000001</v>
       </c>
-      <c r="Q334" s="22">
+      <c r="Q334">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>307.22316000000001</v>
       </c>
@@ -30732,7 +30473,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.92624000000001</v>
       </c>
-      <c r="Q335" s="22">
+      <c r="Q335">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.06250999999997</v>
       </c>
@@ -30786,7 +30527,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>142.21912</v>
       </c>
-      <c r="Q336" s="22">
+      <c r="Q336">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>252.94338999999999</v>
       </c>
@@ -30822,7 +30563,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q337" s="22">
+      <c r="Q337">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -30873,7 +30614,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q338" s="22">
+      <c r="Q338">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -30942,7 +30683,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.90086000000002</v>
       </c>
-      <c r="Q339" s="22">
+      <c r="Q339">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>295.07328000000007</v>
       </c>
@@ -31011,7 +30752,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.1628</v>
       </c>
-      <c r="Q340" s="22">
+      <c r="Q340">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>297.44422500000002</v>
       </c>
@@ -31080,7 +30821,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.3158</v>
       </c>
-      <c r="Q341" s="22">
+      <c r="Q341">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>291.06596999999999</v>
       </c>
@@ -31149,7 +30890,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>172.03997999999999</v>
       </c>
-      <c r="Q342" s="22">
+      <c r="Q342">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>306.72128199999997</v>
       </c>
@@ -31203,7 +30944,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.96621999999999</v>
       </c>
-      <c r="Q343" s="22">
+      <c r="Q343">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>319.30719399999998</v>
       </c>
@@ -31239,7 +30980,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q344" s="22">
+      <c r="Q344">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -31290,7 +31031,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q345" s="22">
+      <c r="Q345">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -31359,7 +31100,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.98736</v>
       </c>
-      <c r="Q346" s="22">
+      <c r="Q346">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>307.20870000000002</v>
       </c>
@@ -31428,7 +31169,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.02438000000001</v>
       </c>
-      <c r="Q347" s="22">
+      <c r="Q347">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>313.41226</v>
       </c>
@@ -31497,7 +31238,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.60560000000001</v>
       </c>
-      <c r="Q348" s="22">
+      <c r="Q348">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>316.53751500000004</v>
       </c>
@@ -31566,7 +31307,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>174.75017</v>
       </c>
-      <c r="Q349" s="22">
+      <c r="Q349">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>321.35136</v>
       </c>
@@ -31620,7 +31361,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>168.95641000000001</v>
       </c>
-      <c r="Q350" s="22">
+      <c r="Q350">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>296.97055999999998</v>
       </c>
@@ -31656,7 +31397,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q351" s="22">
+      <c r="Q351">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -31707,7 +31448,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q352" s="22">
+      <c r="Q352">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -31776,7 +31517,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.51043999999999</v>
       </c>
-      <c r="Q353" s="22">
+      <c r="Q353">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>300.07872300000002</v>
       </c>
@@ -31845,7 +31586,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.49204</v>
       </c>
-      <c r="Q354" s="22">
+      <c r="Q354">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>323.35688700000003</v>
       </c>
@@ -31914,7 +31655,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>176.61847999999998</v>
       </c>
-      <c r="Q355" s="22">
+      <c r="Q355">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>318.32083499999999</v>
       </c>
@@ -31983,7 +31724,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>170.96970000000002</v>
       </c>
-      <c r="Q356" s="22">
+      <c r="Q356">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>310.43387200000001</v>
       </c>
@@ -32037,7 +31778,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>245.17151999999999</v>
       </c>
-      <c r="Q357" s="22">
+      <c r="Q357">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>427.386796</v>
       </c>
@@ -32073,7 +31814,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q358" s="22">
+      <c r="Q358">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -32124,7 +31865,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q359" s="22">
+      <c r="Q359">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -32193,7 +31934,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.96441000000002</v>
       </c>
-      <c r="Q360" s="22">
+      <c r="Q360">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>301.30976599999997</v>
       </c>
@@ -32262,7 +32003,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>169.32533000000001</v>
       </c>
-      <c r="Q361" s="22">
+      <c r="Q361">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>289.62086399999998</v>
       </c>
@@ -32331,7 +32072,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>173.31225000000001</v>
       </c>
-      <c r="Q362" s="22">
+      <c r="Q362">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>311.01734299999998</v>
       </c>
@@ -32400,7 +32141,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>171.55151999999998</v>
       </c>
-      <c r="Q363" s="22">
+      <c r="Q363">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>298.89822100000004</v>
       </c>
@@ -32454,7 +32195,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>154.04160000000002</v>
       </c>
-      <c r="Q364" s="22">
+      <c r="Q364">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>278.68044600000002</v>
       </c>
@@ -32490,7 +32231,7 @@
         <f>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</f>
         <v>0</v>
       </c>
-      <c r="Q365" s="22">
+      <c r="Q365">
         <f>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</f>
         <v>0</v>
       </c>
@@ -32785,7 +32526,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -33350,6 +33090,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/datos/fab_queso_sim.xlsx
+++ b/datos/fab_queso_sim.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="176" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43653533-5B85-4CD1-86B1-0B3D51C280A4}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20642B36-B1ED-4D65-A4FD-93209E7EFA57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
   </bookViews>
   <sheets>
     <sheet name="fab_queso_sim" sheetId="1" r:id="rId1"/>
     <sheet name="BM sencillo" sheetId="2" r:id="rId2"/>
     <sheet name="BM MG TD" sheetId="4" r:id="rId3"/>
+    <sheet name="BM MP TD" sheetId="5" r:id="rId4"/>
+    <sheet name="TD rendim" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
   <si>
     <t>fecha</t>
   </si>
@@ -212,15 +214,31 @@
   <si>
     <t>queso_est_kg</t>
   </si>
+  <si>
+    <t>Suma de entrada_prot_kg</t>
+  </si>
+  <si>
+    <t>Suma de cuba_fab_prot_kg</t>
+  </si>
+  <si>
+    <t>Etiquetas de fila</t>
+  </si>
+  <si>
+    <t>Suma de Rendim (L/kg)</t>
+  </si>
+  <si>
+    <t>Suma de EST (%)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
     <numFmt numFmtId="166" formatCode="#,##0.0_ ;[Red]\-#,##0.0\ "/>
+    <numFmt numFmtId="167" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -771,7 +789,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -806,6 +824,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -852,7 +875,13 @@
     <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="25">
+    <dxf>
+      <alignment horizontal="general"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -937,6 +966,3047 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[fab_queso_sim.xlsx]TD rendim!TablaDinámica1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TD rendim'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Suma de Rendim (L/kg)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TD rendim'!$A$4:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TD rendim'!$B$4:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0.00_ ;[Red]\-#,##0.00\ </c:formatCode>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>8.5925321308382454</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.4627009204561059</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3391525331853824</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5966793521302467</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.5356136362852411</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.4086099913791053</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5702965564733962</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.4982714736162279</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.4886551508936083</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.5580589620897634</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.5047505484076176</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.4425556475523305</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.6061121502157771</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.578786912343153</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.4959861342425</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.6128565188830759</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.4248451663805337</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.4595769228247963</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.3467634292720074</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.5361796318551875</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.3774768801733384</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.2734812642096358</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.4116166478695025</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.4691929626949474</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.3999791256246024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.5750220441977625</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8.3519497023610469</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5408507678037715</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.3390291743626754</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.5109318359758994</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.4096253278127513</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.5439994126069223</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8.5014643670680119</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8.5167421374140222</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8.3137117125029985</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.4716971764555691</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8.6007595042356968</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8.6021395510416774</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8.345706227509968</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8.5859322281036672</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8.4186789439067926</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.5399956462767292</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.4656731004153443</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.4680395507650168</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.567021536072664</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.5034127408993569</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8.6785636234497083</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8.4410770778156365</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8.6513192833624011</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8.4051223135985236</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8.5812126924285259</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8.5657730868509496</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-622C-45E0-944D-9DD934A380D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TD rendim'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Suma de EST (%)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TD rendim'!$A$4:$A$56</c:f>
+              <c:strCache>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TD rendim'!$C$4:$C$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>0.52699224477643891</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.52093436007373872</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52452011370557072</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.52306823973423611</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.51942986033259408</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5273420294200829</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52582391098589076</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.51859308831198436</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.52439853540680514</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.52496663990732817</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.52708840678461044</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.50709130939661184</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.51451801419900545</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.51964364015459374</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.52442633851991582</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.52626022430639385</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.5193749668999752</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5227203315000426</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.51519009995946263</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.51455234486926171</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.51869450489737057</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.53132142319012365</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.52071251891178172</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.53238094276050174</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.52644291217106554</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.52483300477795169</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.51765034178315839</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.51746691744821183</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.51709506575914699</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.51200874926276074</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.51559170862444015</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.51526854326517124</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.52541216611074959</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.51661916189677803</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.51091401642473233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.51943052350116681</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.51838583371586755</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.54174447282647564</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.52146446720912887</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.52344849898779577</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.52215226439913565</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.53166875667710434</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.52239785779243708</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.51549603827407597</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.52678281064814347</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.51773493944057802</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.50789555981259904</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.51539365822930194</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.51723306859725282</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.52405014335335676</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.52767110053408739</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.51469315169520424</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-622C-45E0-944D-9DD934A380D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1485114783"/>
+        <c:axId val="1485114303"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1485114783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1485114303"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1485114303"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0.00_ ;[Red]\-#,##0.00\ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1485114783"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>"EST'</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'TD rendim'!$C$4:$C$55</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>0.52699224477643891</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.52093436007373872</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.52452011370557072</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.52306823973423611</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.51942986033259408</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5273420294200829</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52582391098589076</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.51859308831198436</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.52439853540680514</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.52496663990732817</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.52708840678461044</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.50709130939661184</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.51451801419900545</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.51964364015459374</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.52442633851991582</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.52626022430639385</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.5193749668999752</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.5227203315000426</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.51519009995946263</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.51455234486926171</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.51869450489737057</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.53132142319012365</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.52071251891178172</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.53238094276050174</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.52644291217106554</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.52483300477795169</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.51765034178315839</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.51746691744821183</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.51709506575914699</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.51200874926276074</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.51559170862444015</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.51526854326517124</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.52541216611074959</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.51661916189677803</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.51091401642473233</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.51943052350116681</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.51838583371586755</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.54174447282647564</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.52146446720912887</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.52344849898779577</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.52215226439913565</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.53166875667710434</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.52239785779243708</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.51549603827407597</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.52678281064814347</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.51773493944057802</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.50789555981259904</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.51539365822930194</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.51723306859725282</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.52405014335335676</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.52767110053408739</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.51469315169520424</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'TD rendim'!$B$4:$B$55</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>8.5925321308382454</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.4627009204561059</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.3391525331853824</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.5966793521302467</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8.5356136362852411</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.4086099913791053</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5702965564733962</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.4982714736162279</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.4886551508936083</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.5580589620897634</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>8.5047505484076176</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8.4425556475523305</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8.6061121502157771</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8.578786912343153</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.4959861342425</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.6128565188830759</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.4248451663805337</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>8.4595769228247963</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>8.3467634292720074</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.5361796318551875</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>8.3774768801733384</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>8.2734812642096358</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.4116166478695025</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.4691929626949474</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.3999791256246024</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>8.5750220441977625</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>8.3519497023610469</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.5408507678037715</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.3390291743626754</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.5109318359758994</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.4096253278127513</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>8.5439994126069223</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8.5014643670680119</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>8.5167421374140222</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>8.3137117125029985</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>8.4716971764555691</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>8.6007595042356968</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>8.6021395510416774</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>8.345706227509968</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8.5859322281036672</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8.4186789439067926</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.5399956462767292</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.4656731004153443</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.4680395507650168</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.567021536072664</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.5034127408993569</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8.6785636234497083</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8.4410770778156365</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8.6513192833624011</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8.4051223135985236</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>8.5812126924285259</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>8.5657730868509496</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D007-4CF9-A71F-3845435CB365}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="47711119"/>
+        <c:axId val="47718799"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="47711119"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>EST</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="47718799"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="47718799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Rendimiento</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t> (L/kg)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-ES"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="47711119"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D492087-E903-6002-AF64-08081EBA8D8B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A273F68-29C5-07AB-77AC-83BF75785545}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
@@ -946,7 +4016,7 @@
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla2"/>
   </cacheSource>
-  <cacheFields count="32">
+  <cacheFields count="34">
     <cacheField name="fecha" numFmtId="14">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-12-31T00:00:00" maxDate="2024-12-29T00:00:00" count="364">
         <d v="2023-12-31T00:00:00"/>
@@ -1371,7 +4441,60 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="52"/>
     </cacheField>
     <cacheField name="semana" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="52"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="52" count="52">
+        <n v="1"/>
+        <n v="2"/>
+        <n v="3"/>
+        <n v="4"/>
+        <n v="5"/>
+        <n v="6"/>
+        <n v="7"/>
+        <n v="8"/>
+        <n v="9"/>
+        <n v="10"/>
+        <n v="11"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="14"/>
+        <n v="15"/>
+        <n v="16"/>
+        <n v="17"/>
+        <n v="18"/>
+        <n v="19"/>
+        <n v="20"/>
+        <n v="21"/>
+        <n v="22"/>
+        <n v="23"/>
+        <n v="24"/>
+        <n v="25"/>
+        <n v="26"/>
+        <n v="27"/>
+        <n v="28"/>
+        <n v="29"/>
+        <n v="30"/>
+        <n v="31"/>
+        <n v="32"/>
+        <n v="33"/>
+        <n v="34"/>
+        <n v="35"/>
+        <n v="36"/>
+        <n v="37"/>
+        <n v="38"/>
+        <n v="39"/>
+        <n v="40"/>
+        <n v="41"/>
+        <n v="42"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="45"/>
+        <n v="46"/>
+        <n v="47"/>
+        <n v="48"/>
+        <n v="49"/>
+        <n v="50"/>
+        <n v="51"/>
+        <n v="52"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Meses (fecha)" numFmtId="0" databaseField="0">
       <fieldGroup base="0">
@@ -1427,6 +4550,8 @@
     <cacheField name="Desvicaión queso" numFmtId="0" formula=" (queso_mg_kg-cuba_fab_grasa_kg)/cuba_fab_grasa_kg" databaseField="0"/>
     <cacheField name="Desviacion total" numFmtId="0" formula="queso_mg_kg-entrada_grasa_kg" databaseField="0"/>
     <cacheField name="desv total" numFmtId="0" formula=" (queso_mg_kg-entrada_grasa_kg)/entrada_grasa_kg" databaseField="0"/>
+    <cacheField name="Rendim (L/kg)" numFmtId="0" formula="cuba_fab_litros /queso_kg" databaseField="0"/>
+    <cacheField name="EST (%)" numFmtId="0" formula="queso_est_kg/queso_kg" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -1458,7 +4583,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="52"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="1"/>
@@ -1480,7 +4605,7 @@
     <n v="318.86489699999998"/>
     <n v="154.86700499999998"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="2"/>
@@ -1502,7 +4627,7 @@
     <n v="302.99867"/>
     <n v="166.00428000000002"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="3"/>
@@ -1524,7 +4649,7 @@
     <n v="303.48241499999995"/>
     <n v="157.871285"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="4"/>
@@ -1546,7 +4671,7 @@
     <n v="309.06479999999999"/>
     <n v="160.32736500000001"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="5"/>
@@ -1568,7 +4693,7 @@
     <n v="340.94821500000006"/>
     <n v="172.56207000000003"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="6"/>
@@ -1590,7 +4715,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <n v="1"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="7"/>
@@ -1612,7 +4737,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="8"/>
@@ -1634,7 +4759,7 @@
     <n v="306.54863700000004"/>
     <n v="161.086916"/>
     <n v="2"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="9"/>
@@ -1656,7 +4781,7 @@
     <n v="323.06771200000003"/>
     <n v="165.38563200000002"/>
     <n v="2"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="10"/>
@@ -1678,7 +4803,7 @@
     <n v="302.49744299999998"/>
     <n v="150.52058399999999"/>
     <n v="2"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="11"/>
@@ -1700,7 +4825,7 @@
     <n v="310.48682699999995"/>
     <n v="156.840754"/>
     <n v="2"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="12"/>
@@ -1722,7 +4847,7 @@
     <n v="387.9083"/>
     <n v="205.25244999999998"/>
     <n v="2"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="13"/>
@@ -1744,7 +4869,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="2"/>
-    <n v="2"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="14"/>
@@ -1766,7 +4891,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="2"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="15"/>
@@ -1788,7 +4913,7 @@
     <n v="302.03810399999998"/>
     <n v="167.25734400000002"/>
     <n v="3"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="16"/>
@@ -1810,7 +4935,7 @@
     <n v="314.90581200000003"/>
     <n v="159.94738800000002"/>
     <n v="3"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="17"/>
@@ -1832,7 +4957,7 @@
     <n v="317.22380799999996"/>
     <n v="159.35772800000001"/>
     <n v="3"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="18"/>
@@ -1854,7 +4979,7 @@
     <n v="335.71466500000002"/>
     <n v="172.18210900000003"/>
     <n v="3"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="19"/>
@@ -1876,7 +5001,7 @@
     <n v="375.101856"/>
     <n v="200.99771000000001"/>
     <n v="3"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="20"/>
@@ -1898,7 +5023,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <n v="3"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="21"/>
@@ -1920,7 +5045,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="3"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="22"/>
@@ -1942,7 +5067,7 @@
     <n v="300.159108"/>
     <n v="152.91793800000002"/>
     <n v="4"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="23"/>
@@ -1964,7 +5089,7 @@
     <n v="301.24774400000001"/>
     <n v="157.17273600000001"/>
     <n v="4"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="24"/>
@@ -1986,7 +5111,7 @@
     <n v="317.54294899999996"/>
     <n v="154.36198899999999"/>
     <n v="4"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="25"/>
@@ -2008,7 +5133,7 @@
     <n v="311.991264"/>
     <n v="160.83475199999998"/>
     <n v="4"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="26"/>
@@ -2030,7 +5155,7 @@
     <n v="261.717848"/>
     <n v="131.079928"/>
     <n v="4"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="27"/>
@@ -2052,7 +5177,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="4"/>
-    <n v="4"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="28"/>
@@ -2074,7 +5199,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="4"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="29"/>
@@ -2096,7 +5221,7 @@
     <n v="298.81906399999997"/>
     <n v="158.31283999999997"/>
     <n v="5"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="30"/>
@@ -2118,7 +5243,7 @@
     <n v="315.32410499999992"/>
     <n v="169.44505699999999"/>
     <n v="5"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="31"/>
@@ -2140,7 +5265,7 @@
     <n v="297.84472200000005"/>
     <n v="152.63237699999999"/>
     <n v="5"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="32"/>
@@ -2162,7 +5287,7 @@
     <n v="309.55273100000005"/>
     <n v="164.42546500000003"/>
     <n v="5"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="33"/>
@@ -2184,7 +5309,7 @@
     <n v="284.30212599999999"/>
     <n v="143.31159"/>
     <n v="5"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="34"/>
@@ -2206,7 +5331,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="5"/>
-    <n v="5"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="35"/>
@@ -2228,7 +5353,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="5"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="36"/>
@@ -2250,7 +5375,7 @@
     <n v="314.20863000000003"/>
     <n v="159.53040799999999"/>
     <n v="6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="37"/>
@@ -2272,7 +5397,7 @@
     <n v="318.73766599999993"/>
     <n v="159.27948399999997"/>
     <n v="6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="38"/>
@@ -2294,7 +5419,7 @@
     <n v="321.946415"/>
     <n v="165.97771499999999"/>
     <n v="6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="39"/>
@@ -2316,7 +5441,7 @@
     <n v="317.640128"/>
     <n v="166.80372800000001"/>
     <n v="6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="40"/>
@@ -2338,7 +5463,7 @@
     <n v="275.07363499999997"/>
     <n v="144.844525"/>
     <n v="6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="41"/>
@@ -2360,7 +5485,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="6"/>
-    <n v="6"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="42"/>
@@ -2382,7 +5507,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="6"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="43"/>
@@ -2404,7 +5529,7 @@
     <n v="334.20556199999999"/>
     <n v="171.19346200000001"/>
     <n v="7"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="44"/>
@@ -2426,7 +5551,7 @@
     <n v="310.25231500000001"/>
     <n v="153.92725600000003"/>
     <n v="7"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="45"/>
@@ -2448,7 +5573,7 @@
     <n v="302.04498000000001"/>
     <n v="151.826412"/>
     <n v="7"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="46"/>
@@ -2470,7 +5595,7 @@
     <n v="283.66286400000001"/>
     <n v="161.07345800000002"/>
     <n v="7"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="47"/>
@@ -2492,7 +5617,7 @@
     <n v="442.04370600000004"/>
     <n v="221.27235000000002"/>
     <n v="7"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="48"/>
@@ -2514,7 +5639,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="7"/>
-    <n v="7"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="49"/>
@@ -2536,7 +5661,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="7"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="50"/>
@@ -2558,7 +5683,7 @@
     <n v="294.90070200000002"/>
     <n v="148.89537600000003"/>
     <n v="8"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="51"/>
@@ -2580,7 +5705,7 @@
     <n v="315.35933000000006"/>
     <n v="160.88429500000001"/>
     <n v="8"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="52"/>
@@ -2602,7 +5727,7 @@
     <n v="316.13699699999995"/>
     <n v="166.714517"/>
     <n v="8"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="53"/>
@@ -2624,7 +5749,7 @@
     <n v="286.925276"/>
     <n v="156.21742599999999"/>
     <n v="8"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="54"/>
@@ -2646,7 +5771,7 @@
     <n v="288.27954"/>
     <n v="143.86626000000001"/>
     <n v="8"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="55"/>
@@ -2668,7 +5793,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="8"/>
-    <n v="8"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="56"/>
@@ -2690,7 +5815,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="8"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="57"/>
@@ -2712,7 +5837,7 @@
     <n v="294.99169799999999"/>
     <n v="155.04373200000001"/>
     <n v="9"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="58"/>
@@ -2734,7 +5859,7 @@
     <n v="309.71602200000007"/>
     <n v="153.89616000000001"/>
     <n v="9"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="59"/>
@@ -2756,7 +5881,7 @@
     <n v="288.15526999999997"/>
     <n v="154.42355999999998"/>
     <n v="9"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="60"/>
@@ -2778,7 +5903,7 @@
     <n v="334.80329400000005"/>
     <n v="169.73630999999997"/>
     <n v="9"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="61"/>
@@ -2800,7 +5925,7 @@
     <n v="209.19094699999997"/>
     <n v="108.179254"/>
     <n v="9"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="62"/>
@@ -2822,7 +5947,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="9"/>
-    <n v="9"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="63"/>
@@ -2844,7 +5969,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="9"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="64"/>
@@ -2866,7 +5991,7 @@
     <n v="303.70662799999997"/>
     <n v="149.841228"/>
     <n v="10"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="65"/>
@@ -2888,7 +6013,7 @@
     <n v="315.33957000000004"/>
     <n v="161.53809000000001"/>
     <n v="10"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="66"/>
@@ -2910,7 +6035,7 @@
     <n v="315.61498499999999"/>
     <n v="152.39847"/>
     <n v="10"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="67"/>
@@ -2932,7 +6057,7 @@
     <n v="293.27855999999997"/>
     <n v="158.87846400000001"/>
     <n v="10"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="68"/>
@@ -2954,7 +6079,7 @@
     <n v="263.03376000000003"/>
     <n v="137.69418800000003"/>
     <n v="10"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="69"/>
@@ -2976,7 +6101,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="10"/>
-    <n v="10"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="70"/>
@@ -2998,7 +6123,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="10"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="71"/>
@@ -3020,7 +6145,7 @@
     <n v="318.84832900000004"/>
     <n v="169.45065099999999"/>
     <n v="11"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="72"/>
@@ -3042,7 +6167,7 @@
     <n v="310.32890900000001"/>
     <n v="155.96442400000001"/>
     <n v="11"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="73"/>
@@ -3064,7 +6189,7 @@
     <n v="316.29139200000003"/>
     <n v="160.164072"/>
     <n v="11"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="74"/>
@@ -3086,7 +6211,7 @@
     <n v="300.22355999999996"/>
     <n v="160.67488"/>
     <n v="11"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="75"/>
@@ -3108,7 +6233,7 @@
     <n v="270.48288300000002"/>
     <n v="143.20574400000001"/>
     <n v="11"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="76"/>
@@ -3130,7 +6255,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="11"/>
-    <n v="11"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="77"/>
@@ -3152,7 +6277,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="11"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="78"/>
@@ -3174,7 +6299,7 @@
     <n v="301.451414"/>
     <n v="163.736716"/>
     <n v="12"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="79"/>
@@ -3196,7 +6321,7 @@
     <n v="296.86415"/>
     <n v="163.28117499999999"/>
     <n v="12"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="80"/>
@@ -3218,7 +6343,7 @@
     <n v="308.43467200000003"/>
     <n v="175.58715200000003"/>
     <n v="12"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="81"/>
@@ -3240,7 +6365,7 @@
     <n v="298.36753100000004"/>
     <n v="157.87897999999998"/>
     <n v="12"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="82"/>
@@ -3262,7 +6387,7 @@
     <n v="270.88812000000001"/>
     <n v="146.07182400000002"/>
     <n v="12"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="83"/>
@@ -3284,7 +6409,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="12"/>
-    <n v="12"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="84"/>
@@ -3306,7 +6431,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="12"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="85"/>
@@ -3328,7 +6453,7 @@
     <n v="290.859486"/>
     <n v="149.127599"/>
     <n v="13"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="86"/>
@@ -3350,7 +6475,7 @@
     <n v="317.27373599999999"/>
     <n v="163.056543"/>
     <n v="13"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="87"/>
@@ -3372,7 +6497,7 @@
     <n v="310.67391499999997"/>
     <n v="150.82219499999999"/>
     <n v="13"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="88"/>
@@ -3394,7 +6519,7 @@
     <n v="293.33331000000004"/>
     <n v="151.13731999999999"/>
     <n v="13"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="89"/>
@@ -3416,7 +6541,7 @@
     <n v="336.59479200000004"/>
     <n v="182.10571200000001"/>
     <n v="13"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="90"/>
@@ -3438,7 +6563,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="13"/>
-    <n v="13"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="91"/>
@@ -3460,7 +6585,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="13"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="92"/>
@@ -3482,7 +6607,7 @@
     <n v="287.95120200000002"/>
     <n v="149.188413"/>
     <n v="14"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="93"/>
@@ -3504,7 +6629,7 @@
     <n v="313.23394199999996"/>
     <n v="162.76881599999999"/>
     <n v="14"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="94"/>
@@ -3526,7 +6651,7 @@
     <n v="326.22625599999998"/>
     <n v="156.04209600000002"/>
     <n v="14"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="95"/>
@@ -3548,7 +6673,7 @@
     <n v="296.52183599999995"/>
     <n v="151.18981799999997"/>
     <n v="14"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="96"/>
@@ -3570,7 +6695,7 @@
     <n v="291.36320799999999"/>
     <n v="150.25178599999998"/>
     <n v="14"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="97"/>
@@ -3592,7 +6717,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="14"/>
-    <n v="14"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="98"/>
@@ -3614,7 +6739,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="14"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="99"/>
@@ -3636,7 +6761,7 @@
     <n v="307.77028799999994"/>
     <n v="161.602788"/>
     <n v="15"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="100"/>
@@ -3658,7 +6783,7 @@
     <n v="308.00425000000001"/>
     <n v="156.87065000000001"/>
     <n v="15"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="101"/>
@@ -3680,7 +6805,7 @@
     <n v="327.85602"/>
     <n v="169.43510999999998"/>
     <n v="15"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="102"/>
@@ -3702,7 +6827,7 @@
     <n v="292.68566400000003"/>
     <n v="166.31997600000003"/>
     <n v="15"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="103"/>
@@ -3724,7 +6849,7 @@
     <n v="234.19096399999998"/>
     <n v="119.10712800000002"/>
     <n v="15"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="104"/>
@@ -3746,7 +6871,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="15"/>
-    <n v="15"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="105"/>
@@ -3768,7 +6893,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="15"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="106"/>
@@ -3790,7 +6915,7 @@
     <n v="302.98919799999999"/>
     <n v="154.07841200000001"/>
     <n v="16"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="107"/>
@@ -3812,7 +6937,7 @@
     <n v="319.52921200000003"/>
     <n v="154.141176"/>
     <n v="16"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="108"/>
@@ -3834,7 +6959,7 @@
     <n v="301.69026400000001"/>
     <n v="151.16294400000001"/>
     <n v="16"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="109"/>
@@ -3856,7 +6981,7 @@
     <n v="313.08353999999997"/>
     <n v="159.562242"/>
     <n v="16"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="110"/>
@@ -3878,7 +7003,7 @@
     <n v="292.87780200000003"/>
     <n v="146.720406"/>
     <n v="16"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="111"/>
@@ -3900,7 +7025,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="16"/>
-    <n v="16"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="112"/>
@@ -3922,7 +7047,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="16"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="113"/>
@@ -3944,7 +7069,7 @@
     <n v="300.35292800000002"/>
     <n v="150.234047"/>
     <n v="17"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="114"/>
@@ -3966,7 +7091,7 @@
     <n v="314.060205"/>
     <n v="159.41254499999999"/>
     <n v="17"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="115"/>
@@ -3988,7 +7113,7 @@
     <n v="302.50019800000001"/>
     <n v="154.02587199999999"/>
     <n v="17"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="116"/>
@@ -4010,7 +7135,7 @@
     <n v="328.36831999999993"/>
     <n v="167.55268000000001"/>
     <n v="17"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="117"/>
@@ -4032,7 +7157,7 @@
     <n v="288.52091999999999"/>
     <n v="153.04931999999999"/>
     <n v="17"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="118"/>
@@ -4054,7 +7179,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="17"/>
-    <n v="17"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="119"/>
@@ -4076,7 +7201,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="17"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="120"/>
@@ -4098,7 +7223,7 @@
     <n v="311.041696"/>
     <n v="160.59218000000001"/>
     <n v="18"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="121"/>
@@ -4120,7 +7245,7 @@
     <n v="297.69246399999997"/>
     <n v="146.71821400000002"/>
     <n v="18"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="122"/>
@@ -4142,7 +7267,7 @@
     <n v="309.94915999999995"/>
     <n v="152.94002999999998"/>
     <n v="18"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="123"/>
@@ -4164,7 +7289,7 @@
     <n v="310.87559999999996"/>
     <n v="158.76"/>
     <n v="18"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="124"/>
@@ -4186,7 +7311,7 @@
     <n v="365.25035699999995"/>
     <n v="182.519757"/>
     <n v="18"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="125"/>
@@ -4208,7 +7333,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="18"/>
-    <n v="18"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="126"/>
@@ -4230,7 +7355,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="18"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="127"/>
@@ -4252,7 +7377,7 @@
     <n v="306.22107999999997"/>
     <n v="165.21414000000001"/>
     <n v="19"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="128"/>
@@ -4274,7 +7399,7 @@
     <n v="318.83238"/>
     <n v="156.24008199999997"/>
     <n v="19"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="129"/>
@@ -4296,7 +7421,7 @@
     <n v="303.02731799999998"/>
     <n v="157.89411000000001"/>
     <n v="19"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="130"/>
@@ -4318,7 +7443,7 @@
     <n v="305.37106899999998"/>
     <n v="151.72046599999999"/>
     <n v="19"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="131"/>
@@ -4340,7 +7465,7 @@
     <n v="329.75341000000003"/>
     <n v="179.13805600000001"/>
     <n v="19"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="132"/>
@@ -4362,7 +7487,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="19"/>
-    <n v="19"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="133"/>
@@ -4384,7 +7509,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="19"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="134"/>
@@ -4406,7 +7531,7 @@
     <n v="296.824164"/>
     <n v="156.32229599999999"/>
     <n v="20"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="135"/>
@@ -4428,7 +7553,7 @@
     <n v="299.05250100000006"/>
     <n v="160.233496"/>
     <n v="20"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="136"/>
@@ -4450,7 +7575,7 @@
     <n v="307.88596799999999"/>
     <n v="157.80913200000001"/>
     <n v="20"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="137"/>
@@ -4472,7 +7597,7 @@
     <n v="303.34414500000003"/>
     <n v="160.39989"/>
     <n v="20"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="138"/>
@@ -4494,7 +7619,7 @@
     <n v="308.54831799999999"/>
     <n v="152.341644"/>
     <n v="20"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="139"/>
@@ -4516,7 +7641,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="20"/>
-    <n v="20"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="140"/>
@@ -4538,7 +7663,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="20"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="141"/>
@@ -4560,7 +7685,7 @@
     <n v="306.58225000000004"/>
     <n v="162.25007500000001"/>
     <n v="21"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="142"/>
@@ -4582,7 +7707,7 @@
     <n v="312.31288699999999"/>
     <n v="154.676717"/>
     <n v="21"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="143"/>
@@ -4604,7 +7729,7 @@
     <n v="311.39461000000006"/>
     <n v="169.33434799999998"/>
     <n v="21"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="144"/>
@@ -4626,7 +7751,7 @@
     <n v="314.11743000000001"/>
     <n v="169.228205"/>
     <n v="21"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="145"/>
@@ -4648,7 +7773,7 @@
     <n v="273.32406599999996"/>
     <n v="141.440789"/>
     <n v="21"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="146"/>
@@ -4670,7 +7795,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="21"/>
-    <n v="21"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="147"/>
@@ -4692,7 +7817,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="21"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="148"/>
@@ -4714,7 +7839,7 @@
     <n v="337.90796999999998"/>
     <n v="161.87885999999997"/>
     <n v="22"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="149"/>
@@ -4736,7 +7861,7 @@
     <n v="322.50765000000001"/>
     <n v="163.73926"/>
     <n v="22"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="150"/>
@@ -4758,7 +7883,7 @@
     <n v="319.82082600000001"/>
     <n v="157.44744600000001"/>
     <n v="22"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="151"/>
@@ -4780,7 +7905,7 @@
     <n v="321.52760999999998"/>
     <n v="165.79052999999999"/>
     <n v="22"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="152"/>
@@ -4802,7 +7927,7 @@
     <n v="285.04331399999995"/>
     <n v="156.32455199999998"/>
     <n v="22"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="153"/>
@@ -4824,7 +7949,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="22"/>
-    <n v="22"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="154"/>
@@ -4846,7 +7971,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="22"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="155"/>
@@ -4868,7 +7993,7 @@
     <n v="298.570761"/>
     <n v="158.02928"/>
     <n v="23"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="156"/>
@@ -4890,7 +8015,7 @@
     <n v="318.57291900000001"/>
     <n v="165.38369400000002"/>
     <n v="23"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="157"/>
@@ -4912,7 +8037,7 @@
     <n v="317.40009599999996"/>
     <n v="163.90535999999997"/>
     <n v="23"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="158"/>
@@ -4934,7 +8059,7 @@
     <n v="313.74223999999992"/>
     <n v="154.93294399999996"/>
     <n v="23"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="159"/>
@@ -4956,7 +8081,7 @@
     <n v="266.07095999999996"/>
     <n v="138.25984"/>
     <n v="23"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="160"/>
@@ -4978,7 +8103,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="23"/>
-    <n v="23"/>
+    <x v="22"/>
   </r>
   <r>
     <x v="161"/>
@@ -5000,7 +8125,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="23"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="162"/>
@@ -5022,7 +8147,7 @@
     <n v="307.95287500000001"/>
     <n v="155.22075000000001"/>
     <n v="24"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="163"/>
@@ -5044,7 +8169,7 @@
     <n v="321.44712599999997"/>
     <n v="163.17389399999999"/>
     <n v="24"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="164"/>
@@ -5066,7 +8191,7 @@
     <n v="308.85596599999997"/>
     <n v="159.364304"/>
     <n v="24"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="165"/>
@@ -5088,7 +8213,7 @@
     <n v="338.94638500000002"/>
     <n v="169.688299"/>
     <n v="24"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="166"/>
@@ -5110,7 +8235,7 @@
     <n v="348.69437100000005"/>
     <n v="181.49834100000001"/>
     <n v="24"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="167"/>
@@ -5132,7 +8257,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="24"/>
-    <n v="24"/>
+    <x v="23"/>
   </r>
   <r>
     <x v="168"/>
@@ -5154,7 +8279,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="24"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="169"/>
@@ -5176,7 +8301,7 @@
     <n v="327.47180399999996"/>
     <n v="167.80005"/>
     <n v="25"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="170"/>
@@ -5198,7 +8323,7 @@
     <n v="312.16477800000001"/>
     <n v="158.48914200000002"/>
     <n v="25"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="171"/>
@@ -5220,7 +8345,7 @@
     <n v="313.50006299999995"/>
     <n v="163.48385099999999"/>
     <n v="25"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="172"/>
@@ -5242,7 +8367,7 @@
     <n v="317.39630400000004"/>
     <n v="161.40791999999999"/>
     <n v="25"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="173"/>
@@ -5264,7 +8389,7 @@
     <n v="343.51996200000002"/>
     <n v="179.51602799999998"/>
     <n v="25"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="174"/>
@@ -5286,7 +8411,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="25"/>
-    <n v="25"/>
+    <x v="24"/>
   </r>
   <r>
     <x v="175"/>
@@ -5308,7 +8433,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="25"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="176"/>
@@ -5330,7 +8455,7 @@
     <n v="309.45499999999998"/>
     <n v="159.477"/>
     <n v="26"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="177"/>
@@ -5352,7 +8477,7 @@
     <n v="306.20133999999996"/>
     <n v="146.78814"/>
     <n v="26"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="178"/>
@@ -5374,7 +8499,7 @@
     <n v="291.87752"/>
     <n v="154.29424799999998"/>
     <n v="26"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="179"/>
@@ -5396,7 +8521,7 @@
     <n v="316.76142700000003"/>
     <n v="159.744236"/>
     <n v="26"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="180"/>
@@ -5418,7 +8543,7 @@
     <n v="311.33459500000004"/>
     <n v="167.95144600000003"/>
     <n v="26"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="181"/>
@@ -5440,7 +8565,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="26"/>
-    <n v="26"/>
+    <x v="25"/>
   </r>
   <r>
     <x v="182"/>
@@ -5462,7 +8587,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="26"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="183"/>
@@ -5484,7 +8609,7 @@
     <n v="299.47505000000001"/>
     <n v="170.37877499999999"/>
     <n v="27"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="184"/>
@@ -5506,7 +8631,7 @@
     <n v="314.20612"/>
     <n v="164.41854600000002"/>
     <n v="27"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="185"/>
@@ -5528,7 +8653,7 @@
     <n v="304.83221000000003"/>
     <n v="156.78761599999999"/>
     <n v="27"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="186"/>
@@ -5550,7 +8675,7 @@
     <n v="320.312592"/>
     <n v="162.01713599999999"/>
     <n v="27"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="187"/>
@@ -5572,7 +8697,7 @@
     <n v="309.05207999999999"/>
     <n v="160.55270400000001"/>
     <n v="27"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="188"/>
@@ -5594,7 +8719,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="27"/>
-    <n v="27"/>
+    <x v="26"/>
   </r>
   <r>
     <x v="189"/>
@@ -5616,7 +8741,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="27"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="190"/>
@@ -5638,7 +8763,7 @@
     <n v="318.47215999999997"/>
     <n v="157.36703999999997"/>
     <n v="28"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="191"/>
@@ -5660,7 +8785,7 @@
     <n v="315.36050399999999"/>
     <n v="164.99797600000002"/>
     <n v="28"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="192"/>
@@ -5682,7 +8807,7 @@
     <n v="299.19847100000004"/>
     <n v="157.030731"/>
     <n v="28"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="193"/>
@@ -5704,7 +8829,7 @@
     <n v="295.8279"/>
     <n v="156.94399999999999"/>
     <n v="28"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="194"/>
@@ -5726,7 +8851,7 @@
     <n v="377.85504500000002"/>
     <n v="199.40948799999998"/>
     <n v="28"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="195"/>
@@ -5748,7 +8873,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="28"/>
-    <n v="28"/>
+    <x v="27"/>
   </r>
   <r>
     <x v="196"/>
@@ -5770,7 +8895,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="28"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="197"/>
@@ -5792,7 +8917,7 @@
     <n v="323.13403200000005"/>
     <n v="168.619168"/>
     <n v="29"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="198"/>
@@ -5814,7 +8939,7 @@
     <n v="303.45249000000001"/>
     <n v="158.40042"/>
     <n v="29"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="199"/>
@@ -5836,7 +8961,7 @@
     <n v="310.69316400000002"/>
     <n v="165.64839000000001"/>
     <n v="29"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="200"/>
@@ -5858,7 +8983,7 @@
     <n v="302.68035200000003"/>
     <n v="157.761032"/>
     <n v="29"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="201"/>
@@ -5880,7 +9005,7 @@
     <n v="386.59868799999998"/>
     <n v="204.97662199999999"/>
     <n v="29"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="202"/>
@@ -5902,7 +9027,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="29"/>
-    <n v="29"/>
+    <x v="28"/>
   </r>
   <r>
     <x v="203"/>
@@ -5924,7 +9049,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="29"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="204"/>
@@ -5946,7 +9071,7 @@
     <n v="299.51009999999997"/>
     <n v="158.42743199999998"/>
     <n v="30"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="205"/>
@@ -5968,7 +9093,7 @@
     <n v="298.11462399999999"/>
     <n v="164.45008000000001"/>
     <n v="30"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="206"/>
@@ -5990,7 +9115,7 @@
     <n v="309.64164"/>
     <n v="164.0582"/>
     <n v="30"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="207"/>
@@ -6012,7 +9137,7 @@
     <n v="300.23495100000002"/>
     <n v="162.649485"/>
     <n v="30"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="208"/>
@@ -6034,7 +9159,7 @@
     <n v="276.98101200000002"/>
     <n v="140.14954799999998"/>
     <n v="30"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="209"/>
@@ -6056,7 +9181,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="30"/>
-    <n v="30"/>
+    <x v="29"/>
   </r>
   <r>
     <x v="210"/>
@@ -6078,7 +9203,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="30"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="211"/>
@@ -6100,7 +9225,7 @@
     <n v="304.974917"/>
     <n v="167.45720900000001"/>
     <n v="31"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="212"/>
@@ -6122,7 +9247,7 @@
     <n v="320.44930399999998"/>
     <n v="162.05733599999999"/>
     <n v="31"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="213"/>
@@ -6144,7 +9269,7 @@
     <n v="313.26455999999996"/>
     <n v="158.83585199999999"/>
     <n v="31"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="214"/>
@@ -6166,7 +9291,7 @@
     <n v="299.29727200000002"/>
     <n v="170.57178800000003"/>
     <n v="31"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="215"/>
@@ -6188,7 +9313,7 @@
     <n v="283.72100400000005"/>
     <n v="145.51498800000002"/>
     <n v="31"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="216"/>
@@ -6210,7 +9335,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="31"/>
-    <n v="31"/>
+    <x v="30"/>
   </r>
   <r>
     <x v="217"/>
@@ -6232,7 +9357,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="31"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="218"/>
@@ -6254,7 +9379,7 @@
     <n v="295.400105"/>
     <n v="161.54047700000001"/>
     <n v="32"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="219"/>
@@ -6276,7 +9401,7 @@
     <n v="308.75949800000001"/>
     <n v="157.60276999999999"/>
     <n v="32"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="220"/>
@@ -6298,7 +9423,7 @@
     <n v="302.63360399999999"/>
     <n v="160.95315600000001"/>
     <n v="32"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="221"/>
@@ -6320,7 +9445,7 @@
     <n v="312.468052"/>
     <n v="158.04089599999998"/>
     <n v="32"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="222"/>
@@ -6342,7 +9467,7 @@
     <n v="184.27872599999998"/>
     <n v="99.382626000000002"/>
     <n v="32"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="223"/>
@@ -6364,7 +9489,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="32"/>
-    <n v="32"/>
+    <x v="31"/>
   </r>
   <r>
     <x v="224"/>
@@ -6386,7 +9511,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="32"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="225"/>
@@ -6408,7 +9533,7 @@
     <n v="329.16177499999998"/>
     <n v="162.13974999999999"/>
     <n v="33"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="226"/>
@@ -6430,7 +9555,7 @@
     <n v="299.00382000000002"/>
     <n v="162.33444500000002"/>
     <n v="33"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="227"/>
@@ -6452,7 +9577,7 @@
     <n v="303.27670200000006"/>
     <n v="158.47982999999999"/>
     <n v="33"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="228"/>
@@ -6474,7 +9599,7 @@
     <n v="305.970372"/>
     <n v="165.50325000000001"/>
     <n v="33"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="229"/>
@@ -6496,7 +9621,7 @@
     <n v="312.59525400000001"/>
     <n v="152.97845100000001"/>
     <n v="33"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="230"/>
@@ -6518,7 +9643,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="33"/>
-    <n v="33"/>
+    <x v="32"/>
   </r>
   <r>
     <x v="231"/>
@@ -6540,7 +9665,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="33"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="232"/>
@@ -6562,7 +9687,7 @@
     <n v="312.41502600000001"/>
     <n v="169.46736399999998"/>
     <n v="34"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="233"/>
@@ -6584,7 +9709,7 @@
     <n v="314.11389600000001"/>
     <n v="161.14572000000001"/>
     <n v="34"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="234"/>
@@ -6606,7 +9731,7 @@
     <n v="287.62047999999999"/>
     <n v="160.568772"/>
     <n v="34"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="235"/>
@@ -6628,7 +9753,7 @@
     <n v="297.73619400000001"/>
     <n v="153.03325799999999"/>
     <n v="34"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="236"/>
@@ -6650,7 +9775,7 @@
     <n v="291.796469"/>
     <n v="155.25964200000001"/>
     <n v="34"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="237"/>
@@ -6672,7 +9797,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="34"/>
-    <n v="34"/>
+    <x v="33"/>
   </r>
   <r>
     <x v="238"/>
@@ -6694,7 +9819,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="34"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="239"/>
@@ -6716,7 +9841,7 @@
     <n v="312.50692000000004"/>
     <n v="174.439584"/>
     <n v="35"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="240"/>
@@ -6738,7 +9863,7 @@
     <n v="303.58561200000003"/>
     <n v="158.011843"/>
     <n v="35"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="241"/>
@@ -6760,7 +9885,7 @@
     <n v="319.58390100000003"/>
     <n v="167.78607299999999"/>
     <n v="35"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="242"/>
@@ -6782,7 +9907,7 @@
     <n v="299.30115599999999"/>
     <n v="155.89701599999998"/>
     <n v="35"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="243"/>
@@ -6804,7 +9929,7 @@
     <n v="277.41475499999996"/>
     <n v="152.896188"/>
     <n v="35"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="244"/>
@@ -6826,7 +9951,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="35"/>
-    <n v="35"/>
+    <x v="34"/>
   </r>
   <r>
     <x v="245"/>
@@ -6848,7 +9973,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="35"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="246"/>
@@ -6870,7 +9995,7 @@
     <n v="314.025464"/>
     <n v="163.433548"/>
     <n v="36"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="247"/>
@@ -6892,7 +10017,7 @@
     <n v="290.327832"/>
     <n v="156.28486800000002"/>
     <n v="36"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="248"/>
@@ -6914,7 +10039,7 @@
     <n v="299.44028400000002"/>
     <n v="151.737157"/>
     <n v="36"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="249"/>
@@ -6936,7 +10061,7 @@
     <n v="331.02339199999994"/>
     <n v="177.09503699999996"/>
     <n v="36"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="250"/>
@@ -6958,7 +10083,7 @@
     <n v="229.90438399999999"/>
     <n v="118.588256"/>
     <n v="36"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="251"/>
@@ -6980,7 +10105,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="36"/>
-    <n v="36"/>
+    <x v="35"/>
   </r>
   <r>
     <x v="252"/>
@@ -7002,7 +10127,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="36"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="253"/>
@@ -7024,7 +10149,7 @@
     <n v="301.258152"/>
     <n v="153.666877"/>
     <n v="37"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="254"/>
@@ -7046,7 +10171,7 @@
     <n v="276.231177"/>
     <n v="153.851686"/>
     <n v="37"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="255"/>
@@ -7068,7 +10193,7 @@
     <n v="309.497409"/>
     <n v="164.90050199999999"/>
     <n v="37"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="256"/>
@@ -7090,7 +10215,7 @@
     <n v="316.40519999999998"/>
     <n v="170.5395"/>
     <n v="37"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="257"/>
@@ -7112,7 +10237,7 @@
     <n v="287.25763000000001"/>
     <n v="148.45969000000002"/>
     <n v="37"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="258"/>
@@ -7134,7 +10259,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="37"/>
-    <n v="37"/>
+    <x v="36"/>
   </r>
   <r>
     <x v="259"/>
@@ -7156,7 +10281,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="37"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="260"/>
@@ -7178,7 +10303,7 @@
     <n v="329.38151499999998"/>
     <n v="157.79809"/>
     <n v="38"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="261"/>
@@ -7200,7 +10325,7 @@
     <n v="312.21372999999994"/>
     <n v="149.7921"/>
     <n v="38"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="262"/>
@@ -7222,7 +10347,7 @@
     <n v="309.57350400000001"/>
     <n v="157.87180799999999"/>
     <n v="38"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="263"/>
@@ -7244,7 +10369,7 @@
     <n v="310.18302"/>
     <n v="164.562084"/>
     <n v="38"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="264"/>
@@ -7266,7 +10391,7 @@
     <n v="329.28043000000002"/>
     <n v="166.43843400000003"/>
     <n v="38"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="265"/>
@@ -7288,7 +10413,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="38"/>
-    <n v="38"/>
+    <x v="37"/>
   </r>
   <r>
     <x v="266"/>
@@ -7310,7 +10435,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="38"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="267"/>
@@ -7332,7 +10457,7 @@
     <n v="314.02285499999994"/>
     <n v="165.54826399999999"/>
     <n v="39"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="268"/>
@@ -7354,7 +10479,7 @@
     <n v="322.19748599999997"/>
     <n v="163.10899799999999"/>
     <n v="39"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="269"/>
@@ -7376,7 +10501,7 @@
     <n v="301.44945600000005"/>
     <n v="155.70258000000001"/>
     <n v="39"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="270"/>
@@ -7398,7 +10523,7 @@
     <n v="313.85619999999994"/>
     <n v="164.07771999999997"/>
     <n v="39"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="271"/>
@@ -7420,7 +10545,7 @@
     <n v="357.03544499999998"/>
     <n v="178.00912499999998"/>
     <n v="39"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="272"/>
@@ -7442,7 +10567,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="39"/>
-    <n v="39"/>
+    <x v="38"/>
   </r>
   <r>
     <x v="273"/>
@@ -7464,7 +10589,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="39"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="274"/>
@@ -7486,7 +10611,7 @@
     <n v="302.10578300000003"/>
     <n v="158.15821700000001"/>
     <n v="40"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="275"/>
@@ -7508,7 +10633,7 @@
     <n v="297.47307799999999"/>
     <n v="149.23921599999997"/>
     <n v="40"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="276"/>
@@ -7530,7 +10655,7 @@
     <n v="304.56160899999998"/>
     <n v="165.82788199999999"/>
     <n v="40"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="277"/>
@@ -7552,7 +10677,7 @@
     <n v="313.36451299999999"/>
     <n v="160.22899200000001"/>
     <n v="40"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="278"/>
@@ -7574,7 +10699,7 @@
     <n v="326.14987500000001"/>
     <n v="169.343379"/>
     <n v="40"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="279"/>
@@ -7596,7 +10721,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="40"/>
-    <n v="40"/>
+    <x v="39"/>
   </r>
   <r>
     <x v="280"/>
@@ -7618,7 +10743,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="40"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="281"/>
@@ -7640,7 +10765,7 @@
     <n v="320.98411800000002"/>
     <n v="166.329228"/>
     <n v="41"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="282"/>
@@ -7662,7 +10787,7 @@
     <n v="310.49340999999998"/>
     <n v="146.39165"/>
     <n v="41"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="283"/>
@@ -7684,7 +10809,7 @@
     <n v="306.38069999999999"/>
     <n v="159.79159599999997"/>
     <n v="41"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="284"/>
@@ -7706,7 +10831,7 @@
     <n v="307.72818000000001"/>
     <n v="160.62768"/>
     <n v="41"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="285"/>
@@ -7728,7 +10853,7 @@
     <n v="310.44822600000003"/>
     <n v="160.53241600000001"/>
     <n v="41"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="286"/>
@@ -7750,7 +10875,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="41"/>
-    <n v="41"/>
+    <x v="40"/>
   </r>
   <r>
     <x v="287"/>
@@ -7772,7 +10897,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="41"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="288"/>
@@ -7794,7 +10919,7 @@
     <n v="309.07903800000003"/>
     <n v="157.81536600000001"/>
     <n v="42"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="289"/>
@@ -7816,7 +10941,7 @@
     <n v="313.19079999999997"/>
     <n v="162.07623899999999"/>
     <n v="42"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="290"/>
@@ -7838,7 +10963,7 @@
     <n v="310.49704000000003"/>
     <n v="165.33495500000001"/>
     <n v="42"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="291"/>
@@ -7860,7 +10985,7 @@
     <n v="321.19150400000001"/>
     <n v="170.65530799999999"/>
     <n v="42"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="292"/>
@@ -7882,7 +11007,7 @@
     <n v="333.57794199999995"/>
     <n v="160.51917800000001"/>
     <n v="42"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="293"/>
@@ -7904,7 +11029,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="42"/>
-    <n v="42"/>
+    <x v="41"/>
   </r>
   <r>
     <x v="294"/>
@@ -7926,7 +11051,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="42"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="295"/>
@@ -7948,7 +11073,7 @@
     <n v="321.39113599999996"/>
     <n v="161.46134599999999"/>
     <n v="43"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="296"/>
@@ -7970,7 +11095,7 @@
     <n v="295.66405400000002"/>
     <n v="159.88323299999999"/>
     <n v="43"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="297"/>
@@ -7992,7 +11117,7 @@
     <n v="313.59347500000001"/>
     <n v="160.27450400000001"/>
     <n v="43"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="298"/>
@@ -8014,7 +11139,7 @@
     <n v="312.52327200000002"/>
     <n v="167.98428000000001"/>
     <n v="43"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="299"/>
@@ -8036,7 +11161,7 @@
     <n v="296.31365399999999"/>
     <n v="150.48209399999999"/>
     <n v="43"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="300"/>
@@ -8058,7 +11183,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="43"/>
-    <n v="43"/>
+    <x v="42"/>
   </r>
   <r>
     <x v="301"/>
@@ -8080,7 +11205,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="43"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="302"/>
@@ -8102,7 +11227,7 @@
     <n v="285.85382800000002"/>
     <n v="159.603678"/>
     <n v="44"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="303"/>
@@ -8124,7 +11249,7 @@
     <n v="304.89558"/>
     <n v="157.46057999999999"/>
     <n v="44"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="304"/>
@@ -8146,7 +11271,7 @@
     <n v="323.44878"/>
     <n v="154.40722000000002"/>
     <n v="44"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="305"/>
@@ -8168,7 +11293,7 @@
     <n v="313.97592599999996"/>
     <n v="162.27375299999997"/>
     <n v="44"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="306"/>
@@ -8190,7 +11315,7 @@
     <n v="322.32456000000008"/>
     <n v="168.33510000000001"/>
     <n v="44"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="307"/>
@@ -8212,7 +11337,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="44"/>
-    <n v="44"/>
+    <x v="43"/>
   </r>
   <r>
     <x v="308"/>
@@ -8234,7 +11359,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="44"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="309"/>
@@ -8256,7 +11381,7 @@
     <n v="304.164784"/>
     <n v="150.28910400000001"/>
     <n v="45"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="310"/>
@@ -8278,7 +11403,7 @@
     <n v="301.71225000000004"/>
     <n v="155.68352100000001"/>
     <n v="45"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="311"/>
@@ -8300,7 +11425,7 @@
     <n v="305.83855299999999"/>
     <n v="143.85589200000001"/>
     <n v="45"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="312"/>
@@ -8322,7 +11447,7 @@
     <n v="316.63989600000002"/>
     <n v="166.63334399999999"/>
     <n v="45"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="313"/>
@@ -8344,7 +11469,7 @@
     <n v="305.07240400000001"/>
     <n v="153.048833"/>
     <n v="45"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="314"/>
@@ -8366,7 +11491,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="45"/>
-    <n v="45"/>
+    <x v="44"/>
   </r>
   <r>
     <x v="315"/>
@@ -8388,7 +11513,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="45"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="316"/>
@@ -8410,7 +11535,7 @@
     <n v="298.26641699999999"/>
     <n v="161.524359"/>
     <n v="46"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="317"/>
@@ -8432,7 +11557,7 @@
     <n v="322.010108"/>
     <n v="159.29613000000001"/>
     <n v="46"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="318"/>
@@ -8454,7 +11579,7 @@
     <n v="312.790932"/>
     <n v="153.304877"/>
     <n v="46"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="319"/>
@@ -8476,7 +11601,7 @@
     <n v="291.08916199999999"/>
     <n v="164.33949700000002"/>
     <n v="46"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="320"/>
@@ -8498,7 +11623,7 @@
     <n v="323.24956800000001"/>
     <n v="163.449986"/>
     <n v="46"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="321"/>
@@ -8520,7 +11645,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="46"/>
-    <n v="46"/>
+    <x v="45"/>
   </r>
   <r>
     <x v="322"/>
@@ -8542,7 +11667,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="46"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="323"/>
@@ -8564,7 +11689,7 @@
     <n v="302.07114699999994"/>
     <n v="162.05074899999997"/>
     <n v="47"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="324"/>
@@ -8586,7 +11711,7 @@
     <n v="300.09306600000002"/>
     <n v="156.45877800000002"/>
     <n v="47"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="325"/>
@@ -8608,7 +11733,7 @@
     <n v="287.95486800000003"/>
     <n v="152.328926"/>
     <n v="47"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="326"/>
@@ -8630,7 +11755,7 @@
     <n v="295.51870000000002"/>
     <n v="155.38800000000001"/>
     <n v="47"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="327"/>
@@ -8652,7 +11777,7 @@
     <n v="301.72420799999998"/>
     <n v="158.901408"/>
     <n v="47"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="328"/>
@@ -8674,7 +11799,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="47"/>
-    <n v="47"/>
+    <x v="46"/>
   </r>
   <r>
     <x v="329"/>
@@ -8696,7 +11821,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="47"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="330"/>
@@ -8718,7 +11843,7 @@
     <n v="309.88152500000001"/>
     <n v="166.26623000000001"/>
     <n v="48"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="331"/>
@@ -8740,7 +11865,7 @@
     <n v="309.78547500000002"/>
     <n v="164.20674000000002"/>
     <n v="48"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="332"/>
@@ -8762,7 +11887,7 @@
     <n v="307.22316000000001"/>
     <n v="165.04173299999999"/>
     <n v="48"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="333"/>
@@ -8784,7 +11909,7 @@
     <n v="301.06250999999997"/>
     <n v="160.86270199999998"/>
     <n v="48"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="334"/>
@@ -8806,7 +11931,7 @@
     <n v="252.94338999999999"/>
     <n v="132.93013999999999"/>
     <n v="48"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="335"/>
@@ -8828,7 +11953,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="48"/>
-    <n v="48"/>
+    <x v="47"/>
   </r>
   <r>
     <x v="336"/>
@@ -8850,7 +11975,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="48"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="337"/>
@@ -8872,7 +11997,7 @@
     <n v="295.07328000000007"/>
     <n v="149.87036000000001"/>
     <n v="49"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="338"/>
@@ -8894,7 +12019,7 @@
     <n v="297.44422500000002"/>
     <n v="152.27055000000001"/>
     <n v="49"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="339"/>
@@ -8916,7 +12041,7 @@
     <n v="291.06596999999999"/>
     <n v="159.01148900000001"/>
     <n v="49"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="340"/>
@@ -8938,7 +12063,7 @@
     <n v="306.72128199999997"/>
     <n v="162.10048499999999"/>
     <n v="49"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="341"/>
@@ -8960,7 +12085,7 @@
     <n v="319.30719399999998"/>
     <n v="154.25350399999999"/>
     <n v="49"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="342"/>
@@ -8982,7 +12107,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="49"/>
-    <n v="49"/>
+    <x v="48"/>
   </r>
   <r>
     <x v="343"/>
@@ -9004,7 +12129,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="49"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="344"/>
@@ -9026,7 +12151,7 @@
     <n v="307.20870000000002"/>
     <n v="161.17019999999999"/>
     <n v="50"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="345"/>
@@ -9048,7 +12173,7 @@
     <n v="313.41226"/>
     <n v="154.8682"/>
     <n v="50"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="346"/>
@@ -9070,7 +12195,7 @@
     <n v="316.53751500000004"/>
     <n v="165.44215499999999"/>
     <n v="50"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="347"/>
@@ -9092,7 +12217,7 @@
     <n v="321.35136"/>
     <n v="172.84808000000001"/>
     <n v="50"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="348"/>
@@ -9114,7 +12239,7 @@
     <n v="296.97055999999998"/>
     <n v="152.46937600000001"/>
     <n v="50"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="349"/>
@@ -9136,7 +12261,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <n v="50"/>
+    <x v="49"/>
   </r>
   <r>
     <x v="350"/>
@@ -9158,7 +12283,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="351"/>
@@ -9180,7 +12305,7 @@
     <n v="300.07872300000002"/>
     <n v="157.74039400000001"/>
     <n v="51"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="352"/>
@@ -9202,7 +12327,7 @@
     <n v="323.35688700000003"/>
     <n v="166.22079600000001"/>
     <n v="51"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="353"/>
@@ -9224,7 +12349,7 @@
     <n v="318.32083499999999"/>
     <n v="164.12947499999999"/>
     <n v="51"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="354"/>
@@ -9246,7 +12371,7 @@
     <n v="310.43387200000001"/>
     <n v="168.19099600000001"/>
     <n v="51"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="355"/>
@@ -9268,7 +12393,7 @@
     <n v="427.386796"/>
     <n v="225.67735999999996"/>
     <n v="51"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="356"/>
@@ -9290,7 +12415,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="51"/>
-    <n v="51"/>
+    <x v="50"/>
   </r>
   <r>
     <x v="357"/>
@@ -9312,7 +12437,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="51"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="358"/>
@@ -9334,7 +12459,7 @@
     <n v="301.30976599999997"/>
     <n v="155.48338200000001"/>
     <n v="52"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="359"/>
@@ -9356,7 +12481,7 @@
     <n v="289.62086399999998"/>
     <n v="146.78300999999999"/>
     <n v="52"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="360"/>
@@ -9378,7 +12503,7 @@
     <n v="311.01734299999998"/>
     <n v="170.905868"/>
     <n v="52"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="361"/>
@@ -9400,7 +12525,7 @@
     <n v="298.89822100000004"/>
     <n v="160.37005199999999"/>
     <n v="52"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="362"/>
@@ -9422,7 +12547,7 @@
     <n v="278.68044600000002"/>
     <n v="144.97550100000001"/>
     <n v="52"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
   <r>
     <x v="363"/>
@@ -9444,15 +12569,15 @@
     <n v="0"/>
     <n v="0"/>
     <n v="52"/>
-    <n v="52"/>
+    <x v="51"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEF4566A-639C-45E8-B56D-71F07FA00779}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEF4566A-639C-45E8-B56D-71F07FA00779}" name="TablaDinámica1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
   <location ref="A3:J19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="34">
     <pivotField numFmtId="14" showAll="0">
       <items count="365">
         <item x="0"/>
@@ -9889,6 +13014,8 @@
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="22"/>
@@ -9988,6 +13115,30 @@
     <dataField name="Desviación_x000a_total_x000a_(%)" fld="31" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="14">
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="3"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="3"/>
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
     <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
@@ -10001,34 +13152,28 @@
       </pivotArea>
     </format>
     <format dxfId="21">
+      <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="3"/>
-            <x v="6"/>
+          <reference field="4294967294" count="1">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="4">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="3"/>
-            <x v="6"/>
+          <reference field="4294967294" count="1">
+            <x v="2"/>
           </reference>
         </references>
       </pivotArea>
-    </format>
-    <format dxfId="19">
-      <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="18">
-      <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
@@ -10043,7 +13188,7 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
-            <x v="2"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -10052,7 +13197,7 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
-            <x v="2"/>
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -10070,7 +13215,7 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
-            <x v="4"/>
+            <x v="7"/>
           </reference>
         </references>
       </pivotArea>
@@ -10079,30 +13224,12 @@
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
-            <x v="4"/>
+            <x v="5"/>
           </reference>
         </references>
       </pivotArea>
     </format>
     <format dxfId="11">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="10">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -10124,11 +13251,1224 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BA48B91-167C-452B-88EE-CF82845DDF6C}" name="TablaDinámica1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
+  <location ref="A3:C19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="34">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="365">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item sd="0" x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item sd="0" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="22"/>
+    <field x="20"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Suma de entrada_prot_kg" fld="13" baseField="0" baseItem="0"/>
+    <dataField name="Suma de cuba_fab_prot_kg" fld="15" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="1">
+      <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7369002-1863-45C1-AA48-75EAD51C0863}" name="TablaDinámica1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:C56" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="34">
+    <pivotField numFmtId="14" showAll="0">
+      <items count="365">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item x="294"/>
+        <item x="295"/>
+        <item x="296"/>
+        <item x="297"/>
+        <item x="298"/>
+        <item x="299"/>
+        <item x="300"/>
+        <item x="301"/>
+        <item x="302"/>
+        <item x="303"/>
+        <item x="304"/>
+        <item x="305"/>
+        <item x="306"/>
+        <item x="307"/>
+        <item x="308"/>
+        <item x="309"/>
+        <item x="310"/>
+        <item x="311"/>
+        <item x="312"/>
+        <item x="313"/>
+        <item x="314"/>
+        <item x="315"/>
+        <item x="316"/>
+        <item x="317"/>
+        <item x="318"/>
+        <item x="319"/>
+        <item x="320"/>
+        <item x="321"/>
+        <item x="322"/>
+        <item x="323"/>
+        <item x="324"/>
+        <item x="325"/>
+        <item x="326"/>
+        <item x="327"/>
+        <item x="328"/>
+        <item x="329"/>
+        <item x="330"/>
+        <item x="331"/>
+        <item x="332"/>
+        <item x="333"/>
+        <item x="334"/>
+        <item x="335"/>
+        <item x="336"/>
+        <item x="337"/>
+        <item x="338"/>
+        <item x="339"/>
+        <item x="340"/>
+        <item x="341"/>
+        <item x="342"/>
+        <item x="343"/>
+        <item x="344"/>
+        <item x="345"/>
+        <item x="346"/>
+        <item x="347"/>
+        <item x="348"/>
+        <item x="349"/>
+        <item x="350"/>
+        <item x="351"/>
+        <item x="352"/>
+        <item x="353"/>
+        <item x="354"/>
+        <item x="355"/>
+        <item x="356"/>
+        <item x="357"/>
+        <item x="358"/>
+        <item x="359"/>
+        <item x="360"/>
+        <item x="361"/>
+        <item x="362"/>
+        <item x="363"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="53">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="19"/>
+  </rowFields>
+  <rowItems count="53">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="27"/>
+    </i>
+    <i>
+      <x v="28"/>
+    </i>
+    <i>
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="34"/>
+    </i>
+    <i>
+      <x v="35"/>
+    </i>
+    <i>
+      <x v="36"/>
+    </i>
+    <i>
+      <x v="37"/>
+    </i>
+    <i>
+      <x v="38"/>
+    </i>
+    <i>
+      <x v="39"/>
+    </i>
+    <i>
+      <x v="40"/>
+    </i>
+    <i>
+      <x v="41"/>
+    </i>
+    <i>
+      <x v="42"/>
+    </i>
+    <i>
+      <x v="43"/>
+    </i>
+    <i>
+      <x v="44"/>
+    </i>
+    <i>
+      <x v="45"/>
+    </i>
+    <i>
+      <x v="46"/>
+    </i>
+    <i>
+      <x v="47"/>
+    </i>
+    <i>
+      <x v="48"/>
+    </i>
+    <i>
+      <x v="49"/>
+    </i>
+    <i>
+      <x v="50"/>
+    </i>
+    <i>
+      <x v="51"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Suma de Rendim (L/kg)" fld="32" baseField="0" baseItem="0" numFmtId="167"/>
+    <dataField name="Suma de EST (%)" fld="33" baseField="0" baseItem="0" numFmtId="10"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}" name="Tabla2" displayName="Tabla2" ref="A1:T365" totalsRowShown="0">
   <autoFilter ref="A1:T365" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{B99A55EC-062A-41A1-9987-66C4A77606BA}" name="entrada_kg"/>
     <tableColumn id="3" xr3:uid="{DA11BF6E-5AFF-4E5A-A825-C843AA73522C}" name="entrada_litros"/>
     <tableColumn id="4" xr3:uid="{ED230348-1BB5-43D8-ADE4-81312B15A5A9}" name="entrada_grasa_g_l"/>
@@ -10140,28 +14480,28 @@
     <tableColumn id="10" xr3:uid="{E2106BDF-6A85-4EF5-B55C-0D7CFEBF9BD8}" name="queso_kg"/>
     <tableColumn id="11" xr3:uid="{8A9920A8-F994-40CF-861E-A78626F5DFA0}" name="queso_est_pct"/>
     <tableColumn id="12" xr3:uid="{7BEF460E-C8FD-436F-A522-912A1E3FC0C1}" name="queso_mg_pct"/>
-    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="9">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="6">
+    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="8">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="5">
+    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="7">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="4">
+    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="6">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="3">
+    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="5">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="2">
+    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="4">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_mg_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="1">
+    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.ISOWEEKNUM(Tabla2[[#This Row],[fecha]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -33091,4 +37431,833 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AA94C7-C5BD-465F-A5BD-7EA31E1FE851}">
+  <dimension ref="A3:F19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" customWidth="1"/>
+    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" customWidth="1"/>
+    <col min="11" max="53" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="24">
+        <v>207.85220000000001</v>
+      </c>
+      <c r="C4" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="24">
+        <v>207.85220000000001</v>
+      </c>
+      <c r="C5" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="24">
+        <v>46125.388799999993</v>
+      </c>
+      <c r="C6" s="24">
+        <v>44475.971510000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="24">
+        <v>4189.7649799999999</v>
+      </c>
+      <c r="C7" s="24">
+        <v>4064.6014100000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="24">
+        <v>3678.9864600000005</v>
+      </c>
+      <c r="C8" s="24">
+        <v>3588.1760200000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="24">
+        <v>3694.7668000000003</v>
+      </c>
+      <c r="C9" s="24">
+        <v>3470.6113399999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="24">
+        <v>3900.1222499999999</v>
+      </c>
+      <c r="C10" s="24">
+        <v>3737.1380600000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="24">
+        <v>3896.7146100000004</v>
+      </c>
+      <c r="C11" s="24">
+        <v>3933.1914999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="24">
+        <v>3793.6036499999996</v>
+      </c>
+      <c r="C12" s="24">
+        <v>3459.7737299999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="24">
+        <v>4182.1048700000001</v>
+      </c>
+      <c r="C13" s="24">
+        <v>4025.06646</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="24">
+        <v>3640.0026999999995</v>
+      </c>
+      <c r="C14" s="24">
+        <v>3650.5601099999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="24">
+        <v>3885.3828899999999</v>
+      </c>
+      <c r="C15" s="24">
+        <v>3562.5084399999996</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="24">
+        <v>4081.1784500000008</v>
+      </c>
+      <c r="C16" s="24">
+        <v>3908.5336300000008</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="24">
+        <v>3544.6213400000006</v>
+      </c>
+      <c r="C17" s="24">
+        <v>3582.1439399999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="24">
+        <v>3638.1398000000004</v>
+      </c>
+      <c r="C18" s="24">
+        <v>3493.6668700000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="24">
+        <v>46333.240999999995</v>
+      </c>
+      <c r="C19" s="24">
+        <v>44475.971510000003</v>
+      </c>
+      <c r="E19">
+        <f>C19-B19</f>
+        <v>-1857.2694899999915</v>
+      </c>
+      <c r="F19" s="22">
+        <f>E19/B19</f>
+        <v>-4.0085032903266829E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F055395B-947A-4F92-9BF5-0643DB0D890E}">
+  <dimension ref="A3:C56"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>1</v>
+      </c>
+      <c r="B4" s="25">
+        <v>8.5925321308382454</v>
+      </c>
+      <c r="C4" s="26">
+        <v>0.52699224477643891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>2</v>
+      </c>
+      <c r="B5" s="25">
+        <v>8.4627009204561059</v>
+      </c>
+      <c r="C5" s="26">
+        <v>0.52093436007373872</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>3</v>
+      </c>
+      <c r="B6" s="25">
+        <v>8.3391525331853824</v>
+      </c>
+      <c r="C6" s="26">
+        <v>0.52452011370557072</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>4</v>
+      </c>
+      <c r="B7" s="25">
+        <v>8.5966793521302467</v>
+      </c>
+      <c r="C7" s="26">
+        <v>0.52306823973423611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>5</v>
+      </c>
+      <c r="B8" s="25">
+        <v>8.5356136362852411</v>
+      </c>
+      <c r="C8" s="26">
+        <v>0.51942986033259408</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>6</v>
+      </c>
+      <c r="B9" s="25">
+        <v>8.4086099913791053</v>
+      </c>
+      <c r="C9" s="26">
+        <v>0.5273420294200829</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25">
+        <v>8.5702965564733962</v>
+      </c>
+      <c r="C10" s="26">
+        <v>0.52582391098589076</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>8</v>
+      </c>
+      <c r="B11" s="25">
+        <v>8.4982714736162279</v>
+      </c>
+      <c r="C11" s="26">
+        <v>0.51859308831198436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>9</v>
+      </c>
+      <c r="B12" s="25">
+        <v>8.4886551508936083</v>
+      </c>
+      <c r="C12" s="26">
+        <v>0.52439853540680514</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>10</v>
+      </c>
+      <c r="B13" s="25">
+        <v>8.5580589620897634</v>
+      </c>
+      <c r="C13" s="26">
+        <v>0.52496663990732817</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25">
+        <v>8.5047505484076176</v>
+      </c>
+      <c r="C14" s="26">
+        <v>0.52708840678461044</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>12</v>
+      </c>
+      <c r="B15" s="25">
+        <v>8.4425556475523305</v>
+      </c>
+      <c r="C15" s="26">
+        <v>0.50709130939661184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25">
+        <v>8.6061121502157771</v>
+      </c>
+      <c r="C16" s="26">
+        <v>0.51451801419900545</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25">
+        <v>8.578786912343153</v>
+      </c>
+      <c r="C17" s="26">
+        <v>0.51964364015459374</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25">
+        <v>8.4959861342425</v>
+      </c>
+      <c r="C18" s="26">
+        <v>0.52442633851991582</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25">
+        <v>8.6128565188830759</v>
+      </c>
+      <c r="C19" s="26">
+        <v>0.52626022430639385</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25">
+        <v>8.4248451663805337</v>
+      </c>
+      <c r="C20" s="26">
+        <v>0.5193749668999752</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>18</v>
+      </c>
+      <c r="B21" s="25">
+        <v>8.4595769228247963</v>
+      </c>
+      <c r="C21" s="26">
+        <v>0.5227203315000426</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>19</v>
+      </c>
+      <c r="B22" s="25">
+        <v>8.3467634292720074</v>
+      </c>
+      <c r="C22" s="26">
+        <v>0.51519009995946263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>20</v>
+      </c>
+      <c r="B23" s="25">
+        <v>8.5361796318551875</v>
+      </c>
+      <c r="C23" s="26">
+        <v>0.51455234486926171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>21</v>
+      </c>
+      <c r="B24" s="25">
+        <v>8.3774768801733384</v>
+      </c>
+      <c r="C24" s="26">
+        <v>0.51869450489737057</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>22</v>
+      </c>
+      <c r="B25" s="25">
+        <v>8.2734812642096358</v>
+      </c>
+      <c r="C25" s="26">
+        <v>0.53132142319012365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>23</v>
+      </c>
+      <c r="B26" s="25">
+        <v>8.4116166478695025</v>
+      </c>
+      <c r="C26" s="26">
+        <v>0.52071251891178172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>24</v>
+      </c>
+      <c r="B27" s="25">
+        <v>8.4691929626949474</v>
+      </c>
+      <c r="C27" s="26">
+        <v>0.53238094276050174</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>25</v>
+      </c>
+      <c r="B28" s="25">
+        <v>8.3999791256246024</v>
+      </c>
+      <c r="C28" s="26">
+        <v>0.52644291217106554</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>26</v>
+      </c>
+      <c r="B29" s="25">
+        <v>8.5750220441977625</v>
+      </c>
+      <c r="C29" s="26">
+        <v>0.52483300477795169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>27</v>
+      </c>
+      <c r="B30" s="25">
+        <v>8.3519497023610469</v>
+      </c>
+      <c r="C30" s="26">
+        <v>0.51765034178315839</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
+        <v>28</v>
+      </c>
+      <c r="B31" s="25">
+        <v>8.5408507678037715</v>
+      </c>
+      <c r="C31" s="26">
+        <v>0.51746691744821183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
+        <v>29</v>
+      </c>
+      <c r="B32" s="25">
+        <v>8.3390291743626754</v>
+      </c>
+      <c r="C32" s="26">
+        <v>0.51709506575914699</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
+        <v>30</v>
+      </c>
+      <c r="B33" s="25">
+        <v>8.5109318359758994</v>
+      </c>
+      <c r="C33" s="26">
+        <v>0.51200874926276074</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
+        <v>31</v>
+      </c>
+      <c r="B34" s="25">
+        <v>8.4096253278127513</v>
+      </c>
+      <c r="C34" s="26">
+        <v>0.51559170862444015</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
+        <v>32</v>
+      </c>
+      <c r="B35" s="25">
+        <v>8.5439994126069223</v>
+      </c>
+      <c r="C35" s="26">
+        <v>0.51526854326517124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="17">
+        <v>33</v>
+      </c>
+      <c r="B36" s="25">
+        <v>8.5014643670680119</v>
+      </c>
+      <c r="C36" s="26">
+        <v>0.52541216611074959</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="17">
+        <v>34</v>
+      </c>
+      <c r="B37" s="25">
+        <v>8.5167421374140222</v>
+      </c>
+      <c r="C37" s="26">
+        <v>0.51661916189677803</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="17">
+        <v>35</v>
+      </c>
+      <c r="B38" s="25">
+        <v>8.3137117125029985</v>
+      </c>
+      <c r="C38" s="26">
+        <v>0.51091401642473233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="17">
+        <v>36</v>
+      </c>
+      <c r="B39" s="25">
+        <v>8.4716971764555691</v>
+      </c>
+      <c r="C39" s="26">
+        <v>0.51943052350116681</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="17">
+        <v>37</v>
+      </c>
+      <c r="B40" s="25">
+        <v>8.6007595042356968</v>
+      </c>
+      <c r="C40" s="26">
+        <v>0.51838583371586755</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="17">
+        <v>38</v>
+      </c>
+      <c r="B41" s="25">
+        <v>8.6021395510416774</v>
+      </c>
+      <c r="C41" s="26">
+        <v>0.54174447282647564</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="17">
+        <v>39</v>
+      </c>
+      <c r="B42" s="25">
+        <v>8.345706227509968</v>
+      </c>
+      <c r="C42" s="26">
+        <v>0.52146446720912887</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="17">
+        <v>40</v>
+      </c>
+      <c r="B43" s="25">
+        <v>8.5859322281036672</v>
+      </c>
+      <c r="C43" s="26">
+        <v>0.52344849898779577</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="17">
+        <v>41</v>
+      </c>
+      <c r="B44" s="25">
+        <v>8.4186789439067926</v>
+      </c>
+      <c r="C44" s="26">
+        <v>0.52215226439913565</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="17">
+        <v>42</v>
+      </c>
+      <c r="B45" s="25">
+        <v>8.5399956462767292</v>
+      </c>
+      <c r="C45" s="26">
+        <v>0.53166875667710434</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="17">
+        <v>43</v>
+      </c>
+      <c r="B46" s="25">
+        <v>8.4656731004153443</v>
+      </c>
+      <c r="C46" s="26">
+        <v>0.52239785779243708</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="17">
+        <v>44</v>
+      </c>
+      <c r="B47" s="25">
+        <v>8.4680395507650168</v>
+      </c>
+      <c r="C47" s="26">
+        <v>0.51549603827407597</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="17">
+        <v>45</v>
+      </c>
+      <c r="B48" s="25">
+        <v>8.567021536072664</v>
+      </c>
+      <c r="C48" s="26">
+        <v>0.52678281064814347</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="17">
+        <v>46</v>
+      </c>
+      <c r="B49" s="25">
+        <v>8.5034127408993569</v>
+      </c>
+      <c r="C49" s="26">
+        <v>0.51773493944057802</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="17">
+        <v>47</v>
+      </c>
+      <c r="B50" s="25">
+        <v>8.6785636234497083</v>
+      </c>
+      <c r="C50" s="26">
+        <v>0.50789555981259904</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="17">
+        <v>48</v>
+      </c>
+      <c r="B51" s="25">
+        <v>8.4410770778156365</v>
+      </c>
+      <c r="C51" s="26">
+        <v>0.51539365822930194</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="17">
+        <v>49</v>
+      </c>
+      <c r="B52" s="25">
+        <v>8.6513192833624011</v>
+      </c>
+      <c r="C52" s="26">
+        <v>0.51723306859725282</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="17">
+        <v>50</v>
+      </c>
+      <c r="B53" s="25">
+        <v>8.4051223135985236</v>
+      </c>
+      <c r="C53" s="26">
+        <v>0.52405014335335676</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="17">
+        <v>51</v>
+      </c>
+      <c r="B54" s="25">
+        <v>8.5812126924285259</v>
+      </c>
+      <c r="C54" s="26">
+        <v>0.52767110053408739</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="17">
+        <v>52</v>
+      </c>
+      <c r="B55" s="25">
+        <v>8.5657730868509496</v>
+      </c>
+      <c r="C55" s="26">
+        <v>0.51469315169520424</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B56" s="25">
+        <v>8.4892812388084042</v>
+      </c>
+      <c r="C56" s="26">
+        <v>0.52112736029277018</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/datos/fab_queso_sim.xlsx
+++ b/datos/fab_queso_sim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/34bf2af71bbc2e43/Documentos/GitHub/master-queseria/website/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="242" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E6D1927-757D-45FD-B986-DA23028A4664}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="8_{CF1E59C1-CA92-4C88-887C-A78A793F0426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F257F447-6833-4AFB-8BC2-8A1B8DA37198}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="23595" windowHeight="14250" activeTab="2" xr2:uid="{3820C6B5-2803-4858-AF88-A2FCB3D2881D}"/>
   </bookViews>
   <sheets>
     <sheet name="fab_queso_sim" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>fecha</t>
   </si>
@@ -215,12 +215,6 @@
     <t>queso_est_kg</t>
   </si>
   <si>
-    <t>Suma de entrada_prot_kg</t>
-  </si>
-  <si>
-    <t>Suma de cuba_fab_prot_kg</t>
-  </si>
-  <si>
     <t>Etiquetas de fila</t>
   </si>
   <si>
@@ -228,6 +222,35 @@
   </si>
   <si>
     <t>Suma de EST (%)</t>
+  </si>
+  <si>
+    <t>Entrada en fábrica
+(kg MP)</t>
+  </si>
+  <si>
+    <t>Leche en cubas
+(kg MP)</t>
+  </si>
+  <si>
+    <t>Queso
+(kg ESM)</t>
+  </si>
+  <si>
+    <t>Dif balance cubas
+(kg MP)</t>
+  </si>
+  <si>
+    <t>Dif balance queso
+(kg ESM)</t>
+  </si>
+  <si>
+    <t>Desviación cubas</t>
+  </si>
+  <si>
+    <t>Desviación queso</t>
+  </si>
+  <si>
+    <t>Coef recup MP/ESM</t>
   </si>
 </sst>
 </file>
@@ -376,7 +399,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,6 +589,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -789,7 +818,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -824,10 +853,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Énfasis1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -874,40 +906,7 @@
     <cellStyle name="Título 3" xfId="5" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
@@ -946,6 +945,153 @@
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general"/>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -2301,7 +2447,7 @@
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla2"/>
   </cacheSource>
-  <cacheFields count="34">
+  <cacheFields count="40">
     <cacheField name="fecha" numFmtId="14">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-12-31T00:00:00" maxDate="2024-12-29T00:00:00" count="364">
         <d v="2023-12-31T00:00:00"/>
@@ -2837,6 +2983,12 @@
     <cacheField name="desv total" numFmtId="0" formula=" (queso_mg_kg-entrada_grasa_kg)/entrada_grasa_kg" databaseField="0"/>
     <cacheField name="Rendim (L/kg)" numFmtId="0" formula="cuba_fab_litros/queso_kg" databaseField="0"/>
     <cacheField name="EST (%)" numFmtId="0" formula="queso_est_kg/queso_kg" databaseField="0"/>
+    <cacheField name="queso ESM" numFmtId="0" formula="queso_est_kg-queso_mg_kg" databaseField="0"/>
+    <cacheField name="dif_balance_cubas" numFmtId="0" formula="cuba_fab_prot_kg-entrada_prot_kg" databaseField="0"/>
+    <cacheField name="dif_balance_ESM_queso" numFmtId="0" formula=" (queso_est_kg-queso_mg_kg)-cuba_fab_prot_kg" databaseField="0"/>
+    <cacheField name="dif_balance_MP_pct" numFmtId="0" formula=" (cuba_fab_prot_kg-entrada_prot_kg)/entrada_prot_kg" databaseField="0"/>
+    <cacheField name="dif_balance_MP_queso" numFmtId="0" formula="( (queso_est_kg-queso_mg_kg)-cuba_fab_prot_kg)/cuba_fab_prot_kg" databaseField="0"/>
+    <cacheField name="coef_recup_MP" numFmtId="0" formula=" (queso_est_kg-queso_mg_kg)/cuba_fab_prot_kg" databaseField="0"/>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -10862,7 +11014,7 @@
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DEF4566A-639C-45E8-B56D-71F07FA00779}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
   <location ref="A3:J19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="34">
+  <pivotFields count="40">
     <pivotField numFmtId="14" showAll="0">
       <items count="365">
         <item x="0"/>
@@ -11301,6 +11453,12 @@
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="22"/>
@@ -11400,7 +11558,7 @@
     <dataField name="Desviación_x000a_total_x000a_(%)" fld="31" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="24">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -11412,7 +11570,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -11424,7 +11582,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -11436,13 +11594,13 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="10">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="9">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11451,7 +11609,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11460,7 +11618,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11469,7 +11627,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11478,7 +11636,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11487,7 +11645,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11496,7 +11654,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11505,7 +11663,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11514,7 +11672,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11538,8 +11696,8 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BA48B91-167C-452B-88EE-CF82845DDF6C}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" showError="1" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8" rowHeaderCaption="Mes">
-  <location ref="A3:C19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="34">
+  <location ref="A3:I19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="40">
     <pivotField numFmtId="14" showAll="0">
       <items count="365">
         <item x="0"/>
@@ -11978,6 +12136,12 @@
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="22"/>
@@ -12036,24 +12200,174 @@
   <colFields count="1">
     <field x="-2"/>
   </colFields>
-  <colItems count="2">
+  <colItems count="8">
     <i>
       <x/>
     </i>
     <i i="1">
       <x v="1"/>
     </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+    <i i="4">
+      <x v="4"/>
+    </i>
+    <i i="5">
+      <x v="5"/>
+    </i>
+    <i i="6">
+      <x v="6"/>
+    </i>
+    <i i="7">
+      <x v="7"/>
+    </i>
   </colItems>
-  <dataFields count="2">
-    <dataField name="Suma de entrada_prot_kg" fld="13" baseField="0" baseItem="0"/>
-    <dataField name="Suma de cuba_fab_prot_kg" fld="15" baseField="0" baseItem="0"/>
+  <dataFields count="8">
+    <dataField name="Entrada en fábrica_x000a_(kg MP)" fld="13" baseField="20" baseItem="1" numFmtId="165"/>
+    <dataField name="Leche en cubas_x000a_(kg MP)" fld="15" baseField="20" baseItem="1" numFmtId="165"/>
+    <dataField name="Queso_x000a_(kg ESM)" fld="34" baseField="20" baseItem="7" numFmtId="165"/>
+    <dataField name="Dif balance cubas_x000a_(kg MP)" fld="35" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Dif balance queso_x000a_(kg ESM)" fld="36" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Desviación cubas" fld="37" baseField="20" baseItem="6" numFmtId="164"/>
+    <dataField name="Desviación queso" fld="38" baseField="20" baseItem="11" numFmtId="164"/>
+    <dataField name="Coef recup MP/ESM" fld="39" baseField="20" baseItem="9" numFmtId="164"/>
   </dataFields>
-  <formats count="2">
-    <format dxfId="1">
+  <formats count="16">
+    <format dxfId="38">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="37">
       <pivotArea field="22" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="34">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="33">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="32">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="30">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="24">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -12071,7 +12385,7 @@
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C7369002-1863-45C1-AA48-75EAD51C0863}" name="TablaDinámica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C56" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="34">
+  <pivotFields count="40">
     <pivotField numFmtId="14" showAll="0">
       <items count="365">
         <item x="0"/>
@@ -12537,6 +12851,12 @@
     <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="19"/>
@@ -12753,7 +13073,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}" name="Tabla2" displayName="Tabla2" ref="A1:T365" totalsRowShown="0">
   <autoFilter ref="A1:T365" xr:uid="{4EAA836B-7E28-4F5F-B497-A3F78E114EA5}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{0EAAFB95-0462-4A46-895E-2C8949E731AE}" name="fecha" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{B99A55EC-062A-41A1-9987-66C4A77606BA}" name="entrada_kg"/>
     <tableColumn id="3" xr3:uid="{DA11BF6E-5AFF-4E5A-A825-C843AA73522C}" name="entrada_litros"/>
     <tableColumn id="4" xr3:uid="{ED230348-1BB5-43D8-ADE4-81312B15A5A9}" name="entrada_grasa_g_l"/>
@@ -12765,28 +13085,28 @@
     <tableColumn id="10" xr3:uid="{E2106BDF-6A85-4EF5-B55C-0D7CFEBF9BD8}" name="queso_kg"/>
     <tableColumn id="11" xr3:uid="{8A9920A8-F994-40CF-861E-A78626F5DFA0}" name="queso_est_pct"/>
     <tableColumn id="12" xr3:uid="{7BEF460E-C8FD-436F-A522-912A1E3FC0C1}" name="queso_mg_pct"/>
-    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="9">
+    <tableColumn id="13" xr3:uid="{4C6E2762-B054-43B2-9A21-BCBED25CD3AE}" name="entrada_grasa_kg" dataDxfId="21">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="8">
+    <tableColumn id="14" xr3:uid="{72F3B23C-8C52-4610-8DE2-F2CFF573C1A3}" name="entrada_prot_kg" dataDxfId="20">
       <calculatedColumnFormula>Tabla2[[#This Row],[entrada_litros]]*Tabla2[[#This Row],[entrada_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="7">
+    <tableColumn id="15" xr3:uid="{1F2FDCA1-AA37-432A-9889-51F7AB1D868E}" name="cuba_fab_grasa_kg" dataDxfId="19">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_grasa_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="6">
+    <tableColumn id="16" xr3:uid="{5C5A0D35-AC30-4575-AD36-DFD4AB1AAE78}" name="cuba_fab_prot_kg" dataDxfId="18">
       <calculatedColumnFormula>Tabla2[[#This Row],[cuba_fab_litros]]*Tabla2[[#This Row],[cuba_fab_prot_g_l]]/1000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="5">
+    <tableColumn id="20" xr3:uid="{60870160-690E-43AA-BA91-2F2A23C024EA}" name="queso_est_kg" dataDxfId="17">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_est_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="4">
+    <tableColumn id="19" xr3:uid="{4D671BF4-2751-4C20-94DC-8DF5C5BD43DC}" name="queso_mg_kg" dataDxfId="16">
       <calculatedColumnFormula>Tabla2[[#This Row],[queso_kg]]*Tabla2[[#This Row],[queso_mg_pct]]/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="3">
+    <tableColumn id="17" xr3:uid="{557AB84E-05A8-425D-881C-BCA8985A6A4E}" name="semanaISO" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.ISOWEEKNUM(Tabla2[[#This Row],[fecha]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{4C92060C-D738-42A2-A8B9-D53895DE3195}" name="semana" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -35156,12 +35476,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C76BE22-127F-4554-93CB-9B656134BCAC}">
-  <dimension ref="A3:J19"/>
+  <dimension ref="A3:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" customWidth="1"/>
@@ -35713,6 +36033,45 @@
         <v>-0.19610078607216097</v>
       </c>
     </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C21" s="11">
+        <v>163794.66</v>
+      </c>
+      <c r="D21" s="11">
+        <v>163794.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <f>C19/C21*1000</f>
+        <v>322.18466511667714</v>
+      </c>
+      <c r="D22">
+        <f>D19/D21*1000</f>
+        <v>269.88532068749981</v>
+      </c>
+      <c r="E22">
+        <f>D22/C22</f>
+        <v>0.83767276940310786</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>1308012</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <f>ROUND(C19/C24*1000,3)</f>
+        <v>40.344999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <f>C25*7.967</f>
+        <v>321.42861499999998</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -35720,216 +36079,501 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AA94C7-C5BD-465F-A5BD-7EA31E1FE851}">
-  <dimension ref="A3:F19"/>
+  <dimension ref="A3:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" customWidth="1"/>
-    <col min="9" max="9" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="12.28515625" customWidth="1"/>
     <col min="11" max="53" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="25">
         <v>174.30336</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="25">
+        <v>0</v>
+      </c>
+      <c r="D4" s="25">
+        <v>0</v>
+      </c>
+      <c r="E4" s="25">
+        <v>-174.30336</v>
+      </c>
+      <c r="F4" s="25">
+        <v>0</v>
+      </c>
+      <c r="G4" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="25">
         <v>174.30336</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="25">
+        <v>0</v>
+      </c>
+      <c r="D5" s="25">
+        <v>0</v>
+      </c>
+      <c r="E5" s="25">
+        <v>-174.30336</v>
+      </c>
+      <c r="F5" s="25">
+        <v>0</v>
+      </c>
+      <c r="G5" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="25">
         <v>46307.289270000001</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="25">
         <v>44617.081380000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="25">
+        <v>41042.656793999995</v>
+      </c>
+      <c r="E6" s="25">
+        <v>-1690.2078900000415</v>
+      </c>
+      <c r="F6" s="25">
+        <v>-3574.424586000001</v>
+      </c>
+      <c r="G6" s="19">
+        <v>-3.6499823605417446E-2</v>
+      </c>
+      <c r="H6" s="19">
+        <v>-8.0113366348572246E-2</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.91988663365142775</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="25">
         <v>4044.3596899999998</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="25">
         <v>3900.7101200000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="25">
+        <v>3645.3393879999985</v>
+      </c>
+      <c r="E7" s="25">
+        <v>-143.64956999999958</v>
+      </c>
+      <c r="F7" s="25">
+        <v>-255.37073200000168</v>
+      </c>
+      <c r="G7" s="19">
+        <v>-3.5518495141563335E-2</v>
+      </c>
+      <c r="H7" s="19">
+        <v>-6.5467754368787004E-2</v>
+      </c>
+      <c r="I7" s="19">
+        <v>0.93453224563121295</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="25">
         <v>3825.3529800000006</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="25">
         <v>3635.4073600000002</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="25">
+        <v>3343.5450920000017</v>
+      </c>
+      <c r="E8" s="25">
+        <v>-189.94562000000042</v>
+      </c>
+      <c r="F8" s="25">
+        <v>-291.86226799999849</v>
+      </c>
+      <c r="G8" s="19">
+        <v>-4.9654403395735888E-2</v>
+      </c>
+      <c r="H8" s="19">
+        <v>-8.0283236264339433E-2</v>
+      </c>
+      <c r="I8" s="19">
+        <v>0.91971676373566058</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="25">
         <v>3838.3585999999996</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="25">
         <v>3679.6975400000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="25">
+        <v>3371.889626000002</v>
+      </c>
+      <c r="E9" s="25">
+        <v>-158.66105999999945</v>
+      </c>
+      <c r="F9" s="25">
+        <v>-307.80791399999816</v>
+      </c>
+      <c r="G9" s="19">
+        <v>-4.1335653213850181E-2</v>
+      </c>
+      <c r="H9" s="19">
+        <v>-8.3650330130122089E-2</v>
+      </c>
+      <c r="I9" s="19">
+        <v>0.91634966986987787</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="25">
         <v>3866.9375200000009</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="25">
         <v>3730.6693199999995</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="25">
+        <v>3429.4494379999996</v>
+      </c>
+      <c r="E10" s="25">
+        <v>-136.26820000000134</v>
+      </c>
+      <c r="F10" s="25">
+        <v>-301.21988199999987</v>
+      </c>
+      <c r="G10" s="19">
+        <v>-3.523930740934271E-2</v>
+      </c>
+      <c r="H10" s="19">
+        <v>-8.0741512088774434E-2</v>
+      </c>
+      <c r="I10" s="19">
+        <v>0.91925848791122555</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="25">
         <v>3956.2851999999998</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="25">
         <v>3973.0546899999995</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="25">
+        <v>3614.7037569999998</v>
+      </c>
+      <c r="E11" s="25">
+        <v>16.769489999999678</v>
+      </c>
+      <c r="F11" s="25">
+        <v>-358.35093299999971</v>
+      </c>
+      <c r="G11" s="19">
+        <v>4.2386959362787288E-3</v>
+      </c>
+      <c r="H11" s="19">
+        <v>-9.0195318454073373E-2</v>
+      </c>
+      <c r="I11" s="19">
+        <v>0.90980468154592664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="25">
         <v>3724.5900299999994</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="25">
         <v>3412.9483800000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="25">
+        <v>3126.5458780000013</v>
+      </c>
+      <c r="E12" s="25">
+        <v>-311.64164999999912</v>
+      </c>
+      <c r="F12" s="25">
+        <v>-286.402501999999</v>
+      </c>
+      <c r="G12" s="19">
+        <v>-8.3671396714767865E-2</v>
+      </c>
+      <c r="H12" s="19">
+        <v>-8.3916447045706263E-2</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0.91608355295429378</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="25">
         <v>4055.8208800000002</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="25">
         <v>3942.3746400000009</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="25">
+        <v>3564.0861359999985</v>
+      </c>
+      <c r="E13" s="25">
+        <v>-113.44623999999931</v>
+      </c>
+      <c r="F13" s="25">
+        <v>-378.28850400000238</v>
+      </c>
+      <c r="G13" s="19">
+        <v>-2.7971215533561557E-2</v>
+      </c>
+      <c r="H13" s="19">
+        <v>-9.5954478846790245E-2</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.9040455211532098</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="25">
         <v>3799.4334699999995</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="25">
         <v>3758.2807799999996</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="25">
+        <v>3451.6466340000006</v>
+      </c>
+      <c r="E14" s="25">
+        <v>-41.152689999999893</v>
+      </c>
+      <c r="F14" s="25">
+        <v>-306.63414599999896</v>
+      </c>
+      <c r="G14" s="19">
+        <v>-1.0831270063007551E-2</v>
+      </c>
+      <c r="H14" s="19">
+        <v>-8.158894024942942E-2</v>
+      </c>
+      <c r="I14" s="19">
+        <v>0.91841105975057058</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="25">
         <v>3930.5794900000001</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="25">
         <v>3603.7408199999995</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="25">
+        <v>3345.6104250000003</v>
+      </c>
+      <c r="E15" s="25">
+        <v>-326.83867000000055</v>
+      </c>
+      <c r="F15" s="25">
+        <v>-258.13039499999923</v>
+      </c>
+      <c r="G15" s="19">
+        <v>-8.315279485671985E-2</v>
+      </c>
+      <c r="H15" s="19">
+        <v>-7.1628457176340241E-2</v>
+      </c>
+      <c r="I15" s="19">
+        <v>0.92837154282365975</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="25">
         <v>4083.0744400000003</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="25">
         <v>3954.1513899999995</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D16" s="25">
+        <v>3646.5475340000003</v>
+      </c>
+      <c r="E16" s="25">
+        <v>-128.92305000000079</v>
+      </c>
+      <c r="F16" s="25">
+        <v>-307.60385599999927</v>
+      </c>
+      <c r="G16" s="19">
+        <v>-3.1574993768666335E-2</v>
+      </c>
+      <c r="H16" s="19">
+        <v>-7.7792635046277092E-2</v>
+      </c>
+      <c r="I16" s="19">
+        <v>0.92220736495372291</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="25">
         <v>3599.22417</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="25">
         <v>3588.9856800000002</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D17" s="25">
+        <v>3329.8330930000002</v>
+      </c>
+      <c r="E17" s="25">
+        <v>-10.238489999999729</v>
+      </c>
+      <c r="F17" s="25">
+        <v>-259.15258700000004</v>
+      </c>
+      <c r="G17" s="19">
+        <v>-2.8446380432035519E-3</v>
+      </c>
+      <c r="H17" s="19">
+        <v>-7.2207751745612989E-2</v>
+      </c>
+      <c r="I17" s="19">
+        <v>0.927792248254387</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="25">
         <v>3583.2727999999997</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="25">
         <v>3437.0606600000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D18" s="25">
+        <v>3173.4597930000009</v>
+      </c>
+      <c r="E18" s="25">
+        <v>-146.21213999999964</v>
+      </c>
+      <c r="F18" s="25">
+        <v>-263.6008669999992</v>
+      </c>
+      <c r="G18" s="19">
+        <v>-4.0804077211201904E-2</v>
+      </c>
+      <c r="H18" s="19">
+        <v>-7.669369064903242E-2</v>
+      </c>
+      <c r="I18" s="19">
+        <v>0.92330630935096758</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="25">
         <v>46481.592629999992</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="25">
         <v>44617.081380000003</v>
       </c>
-      <c r="E19">
-        <f>C19-B19</f>
-        <v>-1864.5112499999886</v>
-      </c>
-      <c r="F19" s="22">
-        <f>E19/B19</f>
-        <v>-4.0112895116175565E-2</v>
+      <c r="D19" s="25">
+        <v>41042.656793999995</v>
+      </c>
+      <c r="E19" s="25">
+        <v>-1864.5112500000469</v>
+      </c>
+      <c r="F19" s="25">
+        <v>-3574.424586000001</v>
+      </c>
+      <c r="G19" s="19">
+        <v>-4.0112895116176772E-2</v>
+      </c>
+      <c r="H19" s="19">
+        <v>-8.0113366348572246E-2</v>
+      </c>
+      <c r="I19" s="19">
+        <v>0.91988663365142775</v>
       </c>
     </row>
   </sheetData>
@@ -35948,24 +36592,24 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>55</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>1</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <v>7.8537453585785748</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>0.51116689477398969</v>
       </c>
     </row>
@@ -35973,10 +36617,10 @@
       <c r="A5" s="17">
         <v>2</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="23">
         <v>7.7629752631812439</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>0.51656929573269283</v>
       </c>
     </row>
@@ -35984,10 +36628,10 @@
       <c r="A6" s="17">
         <v>3</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="23">
         <v>7.8420707467854385</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>0.52859152232088746</v>
       </c>
     </row>
@@ -35995,10 +36639,10 @@
       <c r="A7" s="17">
         <v>4</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="23">
         <v>7.8129115169207832</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>0.520026908248584</v>
       </c>
     </row>
@@ -36006,10 +36650,10 @@
       <c r="A8" s="17">
         <v>5</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="23">
         <v>8.2834834507474078</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <v>0.51885661050322274</v>
       </c>
     </row>
@@ -36017,10 +36661,10 @@
       <c r="A9" s="17">
         <v>6</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <v>7.7512498934541147</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <v>0.51608551475623765</v>
       </c>
     </row>
@@ -36028,10 +36672,10 @@
       <c r="A10" s="17">
         <v>7</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="23">
         <v>8.1694603367954546</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="24">
         <v>0.52205727077758413</v>
       </c>
     </row>
@@ -36039,10 +36683,10 @@
       <c r="A11" s="17">
         <v>8</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="23">
         <v>8.1900118109987563</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="24">
         <v>0.52139317993772383</v>
       </c>
     </row>
@@ -36050,10 +36694,10 @@
       <c r="A12" s="17">
         <v>9</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="23">
         <v>7.8282073177122662</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="24">
         <v>0.51578647126461585</v>
       </c>
     </row>
@@ -36061,10 +36705,10 @@
       <c r="A13" s="17">
         <v>10</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="23">
         <v>8.1656607913312413</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>0.52918730198328545</v>
       </c>
     </row>
@@ -36072,10 +36716,10 @@
       <c r="A14" s="17">
         <v>11</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="23">
         <v>7.9373308178164219</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>0.52813039356902636</v>
       </c>
     </row>
@@ -36083,10 +36727,10 @@
       <c r="A15" s="17">
         <v>12</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="23">
         <v>8.0100961247808478</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>0.51944770993289402</v>
       </c>
     </row>
@@ -36094,10 +36738,10 @@
       <c r="A16" s="17">
         <v>13</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="23">
         <v>7.9272144210679754</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>0.51972363192993543</v>
       </c>
     </row>
@@ -36105,10 +36749,10 @@
       <c r="A17" s="17">
         <v>14</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="23">
         <v>7.9518665319551305</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>0.51999782680500506</v>
       </c>
     </row>
@@ -36116,10 +36760,10 @@
       <c r="A18" s="17">
         <v>15</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="23">
         <v>7.9217335891145497</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>0.52087512208490305</v>
       </c>
     </row>
@@ -36127,10 +36771,10 @@
       <c r="A19" s="17">
         <v>16</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="23">
         <v>8.2363370330336672</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>0.53000852271229337</v>
       </c>
     </row>
@@ -36138,10 +36782,10 @@
       <c r="A20" s="17">
         <v>17</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="23">
         <v>8.3247078276864315</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>0.52187494319984362</v>
       </c>
     </row>
@@ -36149,10 +36793,10 @@
       <c r="A21" s="17">
         <v>18</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="23">
         <v>7.9717280465655698</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="24">
         <v>0.52051952965522841</v>
       </c>
     </row>
@@ -36160,10 +36804,10 @@
       <c r="A22" s="17">
         <v>19</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="23">
         <v>8.1151323058453357</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="24">
         <v>0.51881813957170042</v>
       </c>
     </row>
@@ -36171,10 +36815,10 @@
       <c r="A23" s="17">
         <v>20</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="23">
         <v>8.0111079542850856</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="24">
         <v>0.51781293789504879</v>
       </c>
     </row>
@@ -36182,10 +36826,10 @@
       <c r="A24" s="17">
         <v>21</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="23">
         <v>7.9867691360258508</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="24">
         <v>0.51817122287085626</v>
       </c>
     </row>
@@ -36193,10 +36837,10 @@
       <c r="A25" s="17">
         <v>22</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="23">
         <v>8.0288345199128841</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="24">
         <v>0.52132268712508112</v>
       </c>
     </row>
@@ -36204,10 +36848,10 @@
       <c r="A26" s="17">
         <v>23</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="23">
         <v>7.834660982913956</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="24">
         <v>0.51894752121129717</v>
       </c>
     </row>
@@ -36215,10 +36859,10 @@
       <c r="A27" s="17">
         <v>24</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="23">
         <v>8.0814599346317095</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="24">
         <v>0.5155146301683009</v>
       </c>
     </row>
@@ -36226,10 +36870,10 @@
       <c r="A28" s="17">
         <v>25</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="23">
         <v>8.1270438908889773</v>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="24">
         <v>0.52364723260003954</v>
       </c>
     </row>
@@ -36237,10 +36881,10 @@
       <c r="A29" s="17">
         <v>26</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="23">
         <v>8.1647841554683716</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="24">
         <v>0.51583193799742721</v>
       </c>
     </row>
@@ -36248,10 +36892,10 @@
       <c r="A30" s="17">
         <v>27</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="23">
         <v>8.1132335927639865</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="24">
         <v>0.51855133801798481</v>
       </c>
     </row>
@@ -36259,10 +36903,10 @@
       <c r="A31" s="17">
         <v>28</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="23">
         <v>8.1884324053824837</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="24">
         <v>0.51830797331504941</v>
       </c>
     </row>
@@ -36270,10 +36914,10 @@
       <c r="A32" s="17">
         <v>29</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="23">
         <v>8.0555949979031354</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="24">
         <v>0.51851981488146937</v>
       </c>
     </row>
@@ -36281,10 +36925,10 @@
       <c r="A33" s="17">
         <v>30</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B33" s="23">
         <v>7.9381231562044885</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="24">
         <v>0.51376260689346132</v>
       </c>
     </row>
@@ -36292,10 +36936,10 @@
       <c r="A34" s="17">
         <v>31</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B34" s="23">
         <v>7.8315390589432523</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="24">
         <v>0.52129263912321577</v>
       </c>
     </row>
@@ -36303,10 +36947,10 @@
       <c r="A35" s="17">
         <v>32</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B35" s="23">
         <v>7.8062406486799558</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="24">
         <v>0.51155222139099377</v>
       </c>
     </row>
@@ -36314,10 +36958,10 @@
       <c r="A36" s="17">
         <v>33</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B36" s="23">
         <v>8.0995685576352479</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="24">
         <v>0.52684629553000062</v>
       </c>
     </row>
@@ -36325,10 +36969,10 @@
       <c r="A37" s="17">
         <v>34</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B37" s="23">
         <v>8.0329523834176779</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="24">
         <v>0.52270602034609071</v>
       </c>
     </row>
@@ -36336,10 +36980,10 @@
       <c r="A38" s="17">
         <v>35</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B38" s="23">
         <v>7.9260117494497351</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="24">
         <v>0.52619175026610521</v>
       </c>
     </row>
@@ -36347,10 +36991,10 @@
       <c r="A39" s="17">
         <v>36</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="23">
         <v>8.0132875437301401</v>
       </c>
-      <c r="C39" s="25">
+      <c r="C39" s="24">
         <v>0.52369259620630992</v>
       </c>
     </row>
@@ -36358,10 +37002,10 @@
       <c r="A40" s="17">
         <v>37</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B40" s="23">
         <v>7.9942087718969086</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="24">
         <v>0.52030408794411409</v>
       </c>
     </row>
@@ -36369,10 +37013,10 @@
       <c r="A41" s="17">
         <v>38</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B41" s="23">
         <v>8.0582980724024456</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="24">
         <v>0.5149707092932142</v>
       </c>
     </row>
@@ -36380,10 +37024,10 @@
       <c r="A42" s="17">
         <v>39</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="23">
         <v>7.8885880417999257</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="24">
         <v>0.52854331349000439</v>
       </c>
     </row>
@@ -36391,10 +37035,10 @@
       <c r="A43" s="17">
         <v>40</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="23">
         <v>7.9894053537700005</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="24">
         <v>0.51955466849860588</v>
       </c>
     </row>
@@ -36402,10 +37046,10 @@
       <c r="A44" s="17">
         <v>41</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="23">
         <v>7.9683551621054711</v>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="24">
         <v>0.52370677886600481</v>
       </c>
     </row>
@@ -36413,10 +37057,10 @@
       <c r="A45" s="17">
         <v>42</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B45" s="23">
         <v>8.0736429030426677</v>
       </c>
-      <c r="C45" s="25">
+      <c r="C45" s="24">
         <v>0.51534935490713529</v>
       </c>
     </row>
@@ -36424,10 +37068,10 @@
       <c r="A46" s="17">
         <v>43</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B46" s="23">
         <v>7.5598338059112082</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C46" s="24">
         <v>0.5137200470863077</v>
       </c>
     </row>
@@ -36435,10 +37079,10 @@
       <c r="A47" s="17">
         <v>44</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="23">
         <v>8.1400647397751325</v>
       </c>
-      <c r="C47" s="25">
+      <c r="C47" s="24">
         <v>0.52813932451909285</v>
       </c>
     </row>
@@ -36446,10 +37090,10 @@
       <c r="A48" s="17">
         <v>45</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="23">
         <v>8.0504235526452543</v>
       </c>
-      <c r="C48" s="25">
+      <c r="C48" s="24">
         <v>0.52799841525049374</v>
       </c>
     </row>
@@ -36457,10 +37101,10 @@
       <c r="A49" s="17">
         <v>46</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="23">
         <v>7.8423311622370377</v>
       </c>
-      <c r="C49" s="25">
+      <c r="C49" s="24">
         <v>0.51885115248090974</v>
       </c>
     </row>
@@ -36468,10 +37112,10 @@
       <c r="A50" s="17">
         <v>47</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="23">
         <v>7.919104281546427</v>
       </c>
-      <c r="C50" s="25">
+      <c r="C50" s="24">
         <v>0.52040679731773254</v>
       </c>
     </row>
@@ -36479,10 +37123,10 @@
       <c r="A51" s="17">
         <v>48</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="23">
         <v>8.0528646645995323</v>
       </c>
-      <c r="C51" s="25">
+      <c r="C51" s="24">
         <v>0.53140348912098057</v>
       </c>
     </row>
@@ -36490,10 +37134,10 @@
       <c r="A52" s="17">
         <v>49</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="23">
         <v>7.7579292745169521</v>
       </c>
-      <c r="C52" s="25">
+      <c r="C52" s="24">
         <v>0.51977459897921985</v>
       </c>
     </row>
@@ -36501,10 +37145,10 @@
       <c r="A53" s="17">
         <v>50</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B53" s="23">
         <v>7.8468804002670112</v>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="24">
         <v>0.51899110035996576</v>
       </c>
     </row>
@@ -36512,10 +37156,10 @@
       <c r="A54" s="17">
         <v>51</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B54" s="23">
         <v>7.8094140882159317</v>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="24">
         <v>0.518376893958576</v>
       </c>
     </row>
@@ -36523,10 +37167,10 @@
       <c r="A55" s="17">
         <v>52</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B55" s="23">
         <v>8.1563575877142078</v>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="24">
         <v>0.5155860949931016</v>
       </c>
     </row>
@@ -36534,10 +37178,10 @@
       <c r="A56" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B56" s="23">
         <v>7.9856815844912115</v>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="24">
         <v>0.52045915987126778</v>
       </c>
     </row>
